--- a/public/downloads/MandalClassification2023.xlsx
+++ b/public/downloads/MandalClassification2023.xlsx
@@ -1266,16 +1266,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6549578111850476</v>
+        <v>-0.6839074219753485</v>
       </c>
       <c r="O3" s="5">
         <v>32</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1286435409033244</v>
+        <v>0.1275002384859691</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1286435409033244</v>
+        <v>0.1275002384859691</v>
       </c>
       <c r="R3" s="5">
         <v>32</v>
@@ -1325,16 +1325,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.07808067067955018</v>
+        <v>0.2318667792125098</v>
       </c>
       <c r="O4" s="5">
         <v>19</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3846739058295467</v>
+        <v>0.4176280719437523</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.275423763436118</v>
+        <v>0.267329757723857</v>
       </c>
       <c r="R4" s="5">
         <v>19</v>
@@ -1384,16 +1384,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.5603213499452158</v>
+        <v>0.5618896891596776</v>
       </c>
       <c r="O5" s="5">
         <v>17</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2900131910115142</v>
+        <v>0.2902372394707231</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.09914046105831156</v>
+        <v>0.09904820581040204</v>
       </c>
       <c r="R5" s="5">
         <v>17</v>
@@ -1443,16 +1443,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.1992182057704157</v>
+        <v>0.2241605553692843</v>
       </c>
       <c r="O6" s="5">
         <v>19</v>
       </c>
       <c r="P6" s="4">
-        <v>0.3008727891033168</v>
+        <v>0.3013819617637107</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.08868710392837872</v>
+        <v>0.0866243632268279</v>
       </c>
       <c r="R6" s="5">
         <v>19</v>
@@ -1502,16 +1502,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.8701254999113802</v>
+        <v>0.8972111864036521</v>
       </c>
       <c r="O7" s="5">
         <v>15</v>
       </c>
       <c r="P7" s="4">
-        <v>0.7262979343034242</v>
+        <v>0.7305711624389238</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.103221926992926</v>
+        <v>0.0983701717857168</v>
       </c>
       <c r="R7" s="5">
         <v>15</v>
@@ -1561,16 +1561,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.5782420789580899</v>
+        <v>0.6074703115626789</v>
       </c>
       <c r="O8" s="5">
         <v>17</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1128576570727477</v>
+        <v>0.1141031157675313</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.09634525854572218</v>
+        <v>0.09100653514408083</v>
       </c>
       <c r="R8" s="5">
         <v>17</v>
@@ -1620,16 +1620,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.3920123534402298</v>
+        <v>0.4061372664263452</v>
       </c>
       <c r="O9" s="5">
         <v>16</v>
       </c>
       <c r="P9" s="4">
-        <v>0.1030093114182038</v>
+        <v>0.1031555155325643</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.0728467845408195</v>
+        <v>0.07039025625602102</v>
       </c>
       <c r="R9" s="5">
         <v>16</v>
@@ -1679,16 +1679,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.4233600239825325</v>
+        <v>0.4472553836179713</v>
       </c>
       <c r="O10" s="5">
         <v>19</v>
       </c>
       <c r="P10" s="4">
-        <v>0.07666936876749826</v>
+        <v>0.07414799566963043</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.06389927867371058</v>
+        <v>0.06087711082805999</v>
       </c>
       <c r="R10" s="5">
         <v>19</v>
@@ -1738,16 +1738,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>0.2029321400092112</v>
+        <v>0.2330684043262465</v>
       </c>
       <c r="O11" s="5">
         <v>19</v>
       </c>
       <c r="P11" s="4">
-        <v>0.3444204281686378</v>
+        <v>0.3439216264333763</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1324796723591422</v>
+        <v>0.1287561268289021</v>
       </c>
       <c r="R11" s="5">
         <v>19</v>
@@ -1797,16 +1797,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.04868282095612519</v>
+        <v>0.0532704000804074</v>
       </c>
       <c r="O12" s="5">
         <v>16</v>
       </c>
       <c r="P12" s="4">
-        <v>0.3723396907068104</v>
+        <v>0.3728320816406428</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1105029654862515</v>
+        <v>0.1102890575011037</v>
       </c>
       <c r="R12" s="5">
         <v>16</v>
@@ -1856,16 +1856,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.1829994131486766</v>
+        <v>0.2078845448819777</v>
       </c>
       <c r="O13" s="5">
         <v>15</v>
       </c>
       <c r="P13" s="4">
-        <v>0.7519374106465369</v>
+        <v>0.7567216001200084</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1177467815516277</v>
+        <v>0.1144905941211675</v>
       </c>
       <c r="R13" s="5">
         <v>15</v>
@@ -1915,16 +1915,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.2932715123947895</v>
+        <v>0.3093618630188075</v>
       </c>
       <c r="O14" s="5">
         <v>17</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1446951981637435</v>
+        <v>0.1469938196814604</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1155323810078043</v>
+        <v>0.1145858897946267</v>
       </c>
       <c r="R14" s="5">
         <v>17</v>
@@ -1974,16 +1974,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>0.1579458606169233</v>
+        <v>0.1538883869469458</v>
       </c>
       <c r="O15" s="5">
         <v>16</v>
       </c>
       <c r="P15" s="4">
-        <v>0.1276213415993898</v>
+        <v>0.1269304960654491</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.1084942806799867</v>
+        <v>0.1080781974235236</v>
       </c>
       <c r="R15" s="5">
         <v>16</v>
@@ -2033,16 +2033,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.1986485411413518</v>
+        <v>-0.1854240433801628</v>
       </c>
       <c r="O16" s="5">
         <v>19</v>
       </c>
       <c r="P16" s="4">
-        <v>0.1101580487399531</v>
+        <v>0.1073399524747827</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.1194320061391092</v>
+        <v>0.1177093205577302</v>
       </c>
       <c r="R16" s="5">
         <v>19</v>
@@ -2092,16 +2092,16 @@
         <v>0</v>
       </c>
       <c r="N17" s="4">
-        <v>-0.7205926405868297</v>
+        <v>-0.7345170292792318</v>
       </c>
       <c r="O17" s="5">
         <v>13</v>
       </c>
       <c r="P17" s="4">
-        <v>0.2295855595457194</v>
+        <v>0.2275963611610905</v>
       </c>
       <c r="Q17" s="4">
-        <v>0.149469406525432</v>
+        <v>0.1483982997029395</v>
       </c>
       <c r="R17" s="5">
         <v>13</v>
@@ -2151,16 +2151,16 @@
         <v>0</v>
       </c>
       <c r="N18" s="4">
-        <v>-0.575003558138968</v>
+        <v>-0.4594734179697184</v>
       </c>
       <c r="O18" s="5">
         <v>6</v>
       </c>
       <c r="P18" s="4">
-        <v>0.6773923277753833</v>
+        <v>0.7418660035871374</v>
       </c>
       <c r="Q18" s="4">
-        <v>0.2538156420609263</v>
+        <v>0.2502140320626864</v>
       </c>
       <c r="R18" s="5">
         <v>6</v>
@@ -2210,16 +2210,16 @@
         <v>0</v>
       </c>
       <c r="N19" s="4">
-        <v>-0.1393026105712791</v>
+        <v>-0.1182722700391423</v>
       </c>
       <c r="O19" s="5">
         <v>11</v>
       </c>
       <c r="P19" s="4">
-        <v>0.0626988003244912</v>
+        <v>0.06570313468622503</v>
       </c>
       <c r="Q19" s="4">
-        <v>0.0428684574455271</v>
+        <v>0.04095660830624193</v>
       </c>
       <c r="R19" s="5">
         <v>11</v>
@@ -2269,16 +2269,16 @@
         <v>0</v>
       </c>
       <c r="N20" s="4">
-        <v>-0.02204583392430288</v>
+        <v>-0.02387560789454923</v>
       </c>
       <c r="O20" s="5">
         <v>14</v>
       </c>
       <c r="P20" s="4">
-        <v>0.02290286472367844</v>
+        <v>0.02289290328641006</v>
       </c>
       <c r="Q20" s="4">
-        <v>0.02290286472367844</v>
+        <v>0.02289290328641006</v>
       </c>
       <c r="R20" s="5">
         <v>14</v>
@@ -2328,16 +2328,16 @@
         <v>0</v>
       </c>
       <c r="N21" s="4">
-        <v>-0.3115541469745478</v>
+        <v>-0.3064931143369201</v>
       </c>
       <c r="O21" s="5">
         <v>7</v>
       </c>
       <c r="P21" s="4">
-        <v>0.05147844567874809</v>
+        <v>0.05292445500378459</v>
       </c>
       <c r="Q21" s="4">
-        <v>0.04068916987617863</v>
+        <v>0.03996616521366038</v>
       </c>
       <c r="R21" s="5">
         <v>7</v>
@@ -2387,16 +2387,16 @@
         <v>0</v>
       </c>
       <c r="N22" s="4">
-        <v>0.04006638561830616</v>
+        <v>0.06382046914706052</v>
       </c>
       <c r="O22" s="5">
         <v>9</v>
       </c>
       <c r="P22" s="4">
-        <v>0.3547420525079348</v>
+        <v>0.3582211404765303</v>
       </c>
       <c r="Q22" s="4">
-        <v>0.07471266761525948</v>
+        <v>0.06692786916154445</v>
       </c>
       <c r="R22" s="5">
         <v>9</v>
@@ -2446,16 +2446,16 @@
         <v>0</v>
       </c>
       <c r="N23" s="4">
-        <v>0.3573926668226753</v>
+        <v>0.3203765983405233</v>
       </c>
       <c r="O23" s="5">
         <v>9</v>
       </c>
       <c r="P23" s="4">
-        <v>0.2858488001658876</v>
+        <v>0.2699847708163939</v>
       </c>
       <c r="Q23" s="4">
-        <v>0.08650719452724717</v>
+        <v>0.08239429802923029</v>
       </c>
       <c r="R23" s="5">
         <v>9</v>
@@ -2505,7 +2505,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="4">
-        <v>0.3143151757075244</v>
+        <v>0.3274303275425439</v>
       </c>
       <c r="O24" s="5">
         <v>13</v>
@@ -2514,7 +2514,7 @@
         <v>0.2600676560824345</v>
       </c>
       <c r="Q24" s="4">
-        <v>0.1777438199831065</v>
+        <v>0.1767349621496435</v>
       </c>
       <c r="R24" s="5">
         <v>13</v>
@@ -2564,16 +2564,16 @@
         <v>0</v>
       </c>
       <c r="N25" s="4">
-        <v>-0.6105680759296409</v>
+        <v>-0.5754289011058802</v>
       </c>
       <c r="O25" s="5">
         <v>7</v>
       </c>
       <c r="P25" s="4">
-        <v>0.2533062923766995</v>
+        <v>0.2683659387297399</v>
       </c>
       <c r="Q25" s="4">
-        <v>0.08915154543399936</v>
+        <v>0.08413166331631926</v>
       </c>
       <c r="R25" s="5">
         <v>7</v>
@@ -2623,16 +2623,16 @@
         <v>0</v>
       </c>
       <c r="N26" s="4">
-        <v>-0.6807649297984923</v>
+        <v>-0.6303032107161926</v>
       </c>
       <c r="O26" s="5">
         <v>12</v>
       </c>
       <c r="P26" s="4">
-        <v>0.2493662059568564</v>
+        <v>0.2471783958836579</v>
       </c>
       <c r="Q26" s="4">
-        <v>0.1052576558897395</v>
+        <v>0.09429492429062473</v>
       </c>
       <c r="R26" s="5">
         <v>12</v>
@@ -2682,16 +2682,16 @@
         <v>0</v>
       </c>
       <c r="N27" s="4">
-        <v>0.9943378987829945</v>
+        <v>1.014337794341927</v>
       </c>
       <c r="O27" s="5">
         <v>10</v>
       </c>
       <c r="P27" s="4">
-        <v>0.1276248471410761</v>
+        <v>0.1269051097322357</v>
       </c>
       <c r="Q27" s="4">
-        <v>0.07083058020851211</v>
+        <v>0.06582296872434909</v>
       </c>
       <c r="R27" s="5">
         <v>10</v>
@@ -2741,16 +2741,16 @@
         <v>0</v>
       </c>
       <c r="N28" s="4">
-        <v>0.8480019093716261</v>
+        <v>0.8761809894712371</v>
       </c>
       <c r="O28" s="5">
         <v>14</v>
       </c>
       <c r="P28" s="4">
-        <v>0.1048825152503178</v>
+        <v>0.09761187919781784</v>
       </c>
       <c r="Q28" s="4">
-        <v>0.1048825152503178</v>
+        <v>0.09761187919781784</v>
       </c>
       <c r="R28" s="5">
         <v>14</v>
@@ -2800,16 +2800,16 @@
         <v>0</v>
       </c>
       <c r="N29" s="4">
-        <v>0.4710291334233716</v>
+        <v>0.5012753422982712</v>
       </c>
       <c r="O29" s="5">
         <v>7</v>
       </c>
       <c r="P29" s="4">
-        <v>0.09507068766763942</v>
+        <v>0.09286169752421358</v>
       </c>
       <c r="Q29" s="4">
-        <v>0.07144706895603901</v>
+        <v>0.06270820168705882</v>
       </c>
       <c r="R29" s="5">
         <v>7</v>
@@ -2859,16 +2859,16 @@
         <v>0</v>
       </c>
       <c r="N30" s="4">
-        <v>-0.4484751077362269</v>
+        <v>-0.3595700496567389</v>
       </c>
       <c r="O30" s="5">
         <v>5</v>
       </c>
       <c r="P30" s="4">
-        <v>0.8323863230003938</v>
+        <v>0.8776086208797741</v>
       </c>
       <c r="Q30" s="4">
-        <v>0.2055386850287912</v>
+        <v>0.1721320145479773</v>
       </c>
       <c r="R30" s="5">
         <v>5</v>
@@ -2918,16 +2918,16 @@
         <v>0</v>
       </c>
       <c r="N31" s="4">
-        <v>-0.5039956326678577</v>
+        <v>-0.4734155586598234</v>
       </c>
       <c r="O31" s="5">
         <v>10</v>
       </c>
       <c r="P31" s="4">
-        <v>0.2439832534248045</v>
+        <v>0.2490784662727573</v>
       </c>
       <c r="Q31" s="4">
-        <v>0.1235750707809029</v>
+        <v>0.1184763391648232</v>
       </c>
       <c r="R31" s="5">
         <v>10</v>
@@ -2977,16 +2977,16 @@
         <v>0</v>
       </c>
       <c r="N32" s="4">
-        <v>-0.2146864386484803</v>
+        <v>-0.2025832232262701</v>
       </c>
       <c r="O32" s="5">
         <v>9</v>
       </c>
       <c r="P32" s="4">
-        <v>0.3218836725565489</v>
+        <v>0.3236127033311504</v>
       </c>
       <c r="Q32" s="4">
-        <v>0.1293936160938305</v>
+        <v>0.1280488143802516</v>
       </c>
       <c r="R32" s="5">
         <v>9</v>
@@ -3269,16 +3269,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.9767115235602587</v>
+        <v>1.010130588291005</v>
       </c>
       <c r="O3" s="5">
         <v>28</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1526206641424074</v>
+        <v>0.149995322699356</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1576717644327979</v>
+        <v>0.1537591227692537</v>
       </c>
       <c r="R3" s="5">
         <v>28</v>
@@ -3328,16 +3328,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>1.270914285839089</v>
+        <v>0.8740056188378844</v>
       </c>
       <c r="O4" s="5">
         <v>13</v>
       </c>
       <c r="P4" s="4">
-        <v>0.7865020232363858</v>
+        <v>0.6761700656964797</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.7199696604992563</v>
+        <v>0.5758558329386989</v>
       </c>
       <c r="R4" s="5">
         <v>13</v>
@@ -3497,16 +3497,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>1.005422597461194</v>
+        <v>1.027838417320567</v>
       </c>
       <c r="O7" s="5">
         <v>5</v>
       </c>
       <c r="P7" s="4">
-        <v>1.490310894043588</v>
+        <v>1.505648033947369</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.03267079945624345</v>
+        <v>0.02818763548436891</v>
       </c>
       <c r="R7" s="5">
         <v>5</v>
@@ -3556,13 +3556,13 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.7459640073893302</v>
+        <v>0.744870407382848</v>
       </c>
       <c r="O8" s="5">
         <v>12</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3008202379479148</v>
+        <v>0.300382797945322</v>
       </c>
       <c r="Q8" s="4">
         <v>0.1292812734440053</v>
@@ -3615,16 +3615,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.6685103063704408</v>
+        <v>0.6504852249902342</v>
       </c>
       <c r="O9" s="5">
         <v>9</v>
       </c>
       <c r="P9" s="4">
-        <v>0.3980792345819645</v>
+        <v>0.3876436611513187</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1338363099189863</v>
+        <v>0.1318335230989634</v>
       </c>
       <c r="R9" s="5">
         <v>9</v>
@@ -3674,16 +3674,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.5214888869150315</v>
+        <v>0.5538638220947405</v>
       </c>
       <c r="O10" s="5">
         <v>10</v>
       </c>
       <c r="P10" s="4">
-        <v>0.3305246055756507</v>
+        <v>0.3431856390851157</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1250020194624989</v>
+        <v>0.1199205414687441</v>
       </c>
       <c r="R10" s="5">
         <v>10</v>
@@ -3847,16 +3847,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>1.158243869443368</v>
+        <v>1.148039877373051</v>
       </c>
       <c r="O13" s="5">
         <v>6</v>
       </c>
       <c r="P13" s="4">
-        <v>1.543612318650391</v>
+        <v>1.535862349167965</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.05063486959635573</v>
+        <v>0.04861095281900892</v>
       </c>
       <c r="R13" s="5">
         <v>6</v>
@@ -3906,16 +3906,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.2265165791819426</v>
+        <v>0.2174472763281017</v>
       </c>
       <c r="O14" s="5">
         <v>13</v>
       </c>
       <c r="P14" s="4">
-        <v>0.2818479558133734</v>
+        <v>0.2779611117331559</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.09440848724401192</v>
+        <v>0.09371084856294723</v>
       </c>
       <c r="R14" s="5">
         <v>13</v>
@@ -3965,16 +3965,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>0.2603333680664061</v>
+        <v>0.248987768222662</v>
       </c>
       <c r="O15" s="5">
         <v>7</v>
       </c>
       <c r="P15" s="4">
-        <v>0.4144724730859404</v>
+        <v>0.4069087398567777</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.08783135330356591</v>
+        <v>0.08621055332588819</v>
       </c>
       <c r="R15" s="5">
         <v>7</v>
@@ -4024,16 +4024,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>0.3627144155482075</v>
+        <v>0.3599514684033238</v>
       </c>
       <c r="O16" s="5">
         <v>11</v>
       </c>
       <c r="P16" s="4">
-        <v>0.3269450087611547</v>
+        <v>0.3254977507328823</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.1172613546836238</v>
+        <v>0.1170101776704526</v>
       </c>
       <c r="R16" s="5">
         <v>11</v>
@@ -4081,16 +4081,16 @@
         <v>7</v>
       </c>
       <c r="N17" s="4">
-        <v>2.839772191216679</v>
+        <v>2.833014998270244</v>
       </c>
       <c r="O17" s="5">
         <v>7</v>
       </c>
       <c r="P17" s="4">
-        <v>0.3079785223855984</v>
+        <v>0.3068523235611925</v>
       </c>
       <c r="Q17" s="4">
-        <v>0.1241769834789523</v>
+        <v>0.1232116702008901</v>
       </c>
       <c r="R17" s="5">
         <v>7</v>
@@ -4140,16 +4140,16 @@
         <v>0</v>
       </c>
       <c r="N18" s="4">
-        <v>0.1631985743547741</v>
+        <v>0.02905962197752388</v>
       </c>
       <c r="O18" s="5">
         <v>7</v>
       </c>
       <c r="P18" s="4">
-        <v>0.613020261846578</v>
+        <v>0.545950785657953</v>
       </c>
       <c r="Q18" s="4">
-        <v>0.2813354538329085</v>
+        <v>0.2621727463504442</v>
       </c>
       <c r="R18" s="5">
         <v>7</v>
@@ -4199,16 +4199,16 @@
         <v>0</v>
       </c>
       <c r="N19" s="4">
-        <v>0.1509392162089739</v>
+        <v>0.1353504440527331</v>
       </c>
       <c r="O19" s="5">
         <v>5</v>
       </c>
       <c r="P19" s="4">
-        <v>0.3835131725781215</v>
+        <v>0.3723783353236639</v>
       </c>
       <c r="Q19" s="4">
-        <v>0.04921296443124674</v>
+        <v>0.04609520999999859</v>
       </c>
       <c r="R19" s="5">
         <v>5</v>
@@ -4258,16 +4258,16 @@
         <v>0</v>
       </c>
       <c r="N20" s="4">
-        <v>0.04077261365234221</v>
+        <v>0.05486178060546365</v>
       </c>
       <c r="O20" s="5">
         <v>10</v>
       </c>
       <c r="P20" s="4">
-        <v>0.1426149799368952</v>
+        <v>0.1403062284104554</v>
       </c>
       <c r="Q20" s="4">
-        <v>0.05879587571874594</v>
+        <v>0.05156774864843783</v>
       </c>
       <c r="R20" s="5">
         <v>10</v>
@@ -4317,16 +4317,16 @@
         <v>0</v>
       </c>
       <c r="N21" s="4">
-        <v>0.09670718108815939</v>
+        <v>0.09300194996092159</v>
       </c>
       <c r="O21" s="5">
         <v>7</v>
       </c>
       <c r="P21" s="4">
-        <v>0.3106312719770373</v>
+        <v>0.3080860114843692</v>
       </c>
       <c r="Q21" s="4">
-        <v>0.02242418602997406</v>
+        <v>0.02103889617187552</v>
       </c>
       <c r="R21" s="5">
         <v>7</v>
@@ -4376,16 +4376,16 @@
         <v>0</v>
       </c>
       <c r="N22" s="4">
-        <v>0.8635978931119771</v>
+        <v>0.8909706227343861</v>
       </c>
       <c r="O22" s="5">
         <v>6</v>
       </c>
       <c r="P22" s="4">
-        <v>0.7438722826269568</v>
+        <v>0.7557221885198179</v>
       </c>
       <c r="Q22" s="4">
-        <v>0.07413840077258112</v>
+        <v>0.06529120835937856</v>
       </c>
       <c r="R22" s="5">
         <v>6</v>
@@ -4488,16 +4488,16 @@
         <v>0</v>
       </c>
       <c r="N24" s="4">
-        <v>0.4698357895328734</v>
+        <v>0.4530342141162009</v>
       </c>
       <c r="O24" s="5">
         <v>9</v>
       </c>
       <c r="P24" s="4">
-        <v>0.3149474072415863</v>
+        <v>0.3110701206069695</v>
       </c>
       <c r="Q24" s="4">
-        <v>0.1830706950636523</v>
+        <v>0.1812038533506887</v>
       </c>
       <c r="R24" s="5">
         <v>9</v>
@@ -4547,13 +4547,13 @@
         <v>0</v>
       </c>
       <c r="N25" s="4">
-        <v>-0.4224667546907455</v>
+        <v>-0.4176011906542811</v>
       </c>
       <c r="O25" s="5">
         <v>6</v>
       </c>
       <c r="P25" s="4">
-        <v>0.5196541440214392</v>
+        <v>0.5215255148046947</v>
       </c>
       <c r="Q25" s="4">
         <v>0.05703017774739294</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="N26" s="4">
-        <v>-0.307780355939122</v>
+        <v>-0.3015105891162193</v>
       </c>
       <c r="O26" s="5">
         <v>9</v>
@@ -4615,7 +4615,7 @@
         <v>0.3317915062332548</v>
       </c>
       <c r="Q26" s="4">
-        <v>0.1634108483101822</v>
+        <v>0.1627142075520819</v>
       </c>
       <c r="R26" s="5">
         <v>9</v>
@@ -4665,16 +4665,16 @@
         <v>0</v>
       </c>
       <c r="N27" s="4">
-        <v>0.9570787019121099</v>
+        <v>0.9584882831152299</v>
       </c>
       <c r="O27" s="5">
         <v>5</v>
       </c>
       <c r="P27" s="4">
-        <v>0.3588143449591318</v>
+        <v>0.3595733502223503</v>
       </c>
       <c r="Q27" s="4">
-        <v>0.09071392134999315</v>
+        <v>0.09043200510936913</v>
       </c>
       <c r="R27" s="5">
         <v>5</v>
@@ -4724,16 +4724,16 @@
         <v>0</v>
       </c>
       <c r="N28" s="4">
-        <v>0.8330802657801605</v>
+        <v>0.8529201776464674</v>
       </c>
       <c r="O28" s="5">
         <v>9</v>
       </c>
       <c r="P28" s="4">
-        <v>0.1338325449936913</v>
+        <v>0.1356361733451737</v>
       </c>
       <c r="Q28" s="4">
-        <v>0.08748546398341665</v>
+        <v>0.08528102933160477</v>
       </c>
       <c r="R28" s="5">
         <v>9</v>
@@ -4783,16 +4783,16 @@
         <v>0</v>
       </c>
       <c r="N29" s="4">
-        <v>0.7709619078648261</v>
+        <v>0.7438891058447439</v>
       </c>
       <c r="O29" s="5">
         <v>7</v>
       </c>
       <c r="P29" s="4">
-        <v>0.2584380009614657</v>
+        <v>0.2429678283785616</v>
       </c>
       <c r="Q29" s="4">
-        <v>0.1025194763488492</v>
+        <v>0.09865193320312317</v>
       </c>
       <c r="R29" s="5">
         <v>7</v>
@@ -4842,16 +4842,16 @@
         <v>0</v>
       </c>
       <c r="N30" s="4">
-        <v>-0.632612531956375</v>
+        <v>-0.7181822947949286</v>
       </c>
       <c r="O30" s="5">
         <v>9</v>
       </c>
       <c r="P30" s="4">
-        <v>0.5705467668770011</v>
+        <v>0.5264694977884534</v>
       </c>
       <c r="Q30" s="4">
-        <v>0.2897218303124978</v>
+        <v>0.2640856695572861</v>
       </c>
       <c r="R30" s="5">
         <v>9</v>
@@ -4901,13 +4901,13 @@
         <v>0</v>
       </c>
       <c r="N31" s="4">
-        <v>-0.246677168935553</v>
+        <v>-0.2529662213183599</v>
       </c>
       <c r="O31" s="5">
         <v>6</v>
       </c>
       <c r="P31" s="4">
-        <v>0.7515765004687472</v>
+        <v>0.7479827562500004</v>
       </c>
       <c r="Q31" s="4">
         <v>0.05064565118489384</v>
@@ -5197,16 +5197,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.09998699348744744</v>
+        <v>-0.1118664242983209</v>
       </c>
       <c r="O3" s="5">
         <v>32</v>
       </c>
       <c r="P3" s="4">
-        <v>0.075403293171017</v>
+        <v>0.07423650426709916</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.075403293171017</v>
+        <v>0.07423650426709916</v>
       </c>
       <c r="R3" s="5">
         <v>32</v>
@@ -5256,16 +5256,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2588002597350574</v>
+        <v>0.2676249623539491</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2256110125168824</v>
+        <v>0.2262413484182318</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1331835551872752</v>
+        <v>0.1327633312530423</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -5315,16 +5315,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3954132419056317</v>
+        <v>0.3921875264765884</v>
       </c>
       <c r="O5" s="5">
         <v>20</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1280517324404905</v>
+        <v>0.1275673365475919</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.06074833556333233</v>
+        <v>0.06040100564724096</v>
       </c>
       <c r="R5" s="5">
         <v>20</v>
@@ -5374,16 +5374,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.3574198935496803</v>
+        <v>0.3370414269080673</v>
       </c>
       <c r="O6" s="5">
         <v>20</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1419722155239791</v>
+        <v>0.1395753849390488</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.07408961754585178</v>
+        <v>0.07259186876375559</v>
       </c>
       <c r="R6" s="5">
         <v>20</v>
@@ -5433,16 +5433,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.2123326957519699</v>
+        <v>0.2413773820973404</v>
       </c>
       <c r="O7" s="5">
         <v>17</v>
       </c>
       <c r="P7" s="4">
-        <v>0.4468970639060343</v>
+        <v>0.4509122008101348</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.08003922462840164</v>
+        <v>0.07816505578161509</v>
       </c>
       <c r="R7" s="5">
         <v>17</v>
@@ -5492,13 +5492,13 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.5468961906630441</v>
+        <v>0.5567322246527198</v>
       </c>
       <c r="O8" s="5">
         <v>20</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1149749778813158</v>
+        <v>0.1154433604522528</v>
       </c>
       <c r="Q8" s="4">
         <v>0.106165623213802</v>
@@ -5551,16 +5551,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.5356408734340067</v>
+        <v>0.5307633484739043</v>
       </c>
       <c r="O9" s="5">
         <v>17</v>
       </c>
       <c r="P9" s="4">
-        <v>0.124342619288368</v>
+        <v>0.123181303821677</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.09932365302067341</v>
+        <v>0.0990367397877262</v>
       </c>
       <c r="R9" s="5">
         <v>17</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.5328046740263744</v>
+        <v>0.5016589767032542</v>
       </c>
       <c r="O10" s="5">
         <v>15</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1357956474468411</v>
+        <v>0.1254137483391343</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1002415947911626</v>
+        <v>0.0981652149696212</v>
       </c>
       <c r="R10" s="5">
         <v>15</v>
@@ -5669,13 +5669,13 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.006278060027424814</v>
+        <v>0.002872485458883745</v>
       </c>
       <c r="O11" s="5">
         <v>20</v>
       </c>
       <c r="P11" s="4">
-        <v>0.08770214718310439</v>
+        <v>0.08813788744435717</v>
       </c>
       <c r="Q11" s="4">
         <v>0.08638836017973901</v>
@@ -5728,16 +5728,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.05853295146062685</v>
+        <v>0.04535746117875661</v>
       </c>
       <c r="O12" s="5">
         <v>20</v>
       </c>
       <c r="P12" s="4">
-        <v>0.07983189775662536</v>
+        <v>0.07745556281494596</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.08096419314134765</v>
+        <v>0.07912781596667777</v>
       </c>
       <c r="R12" s="5">
         <v>20</v>
@@ -5787,16 +5787,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.2501756412907676</v>
+        <v>-0.259136208361781</v>
       </c>
       <c r="O13" s="5">
         <v>17</v>
       </c>
       <c r="P13" s="4">
-        <v>0.4660993098213174</v>
+        <v>0.4639658414710761</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1114469199989258</v>
+        <v>0.110919827818278</v>
       </c>
       <c r="R13" s="5">
         <v>17</v>
@@ -5846,16 +5846,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.02697907090069691</v>
+        <v>0.04977642172350727</v>
       </c>
       <c r="O14" s="5">
         <v>20</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1370186868169958</v>
+        <v>0.1356328573880217</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1389125505212656</v>
+        <v>0.1363175620797023</v>
       </c>
       <c r="R14" s="5">
         <v>20</v>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>0.005095538480831278</v>
+        <v>0.02133314620041915</v>
       </c>
       <c r="O15" s="5">
         <v>17</v>
       </c>
       <c r="P15" s="4">
-        <v>0.1506572604820762</v>
+        <v>0.1529600833964637</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.1251805040689068</v>
+        <v>0.1242045540879531</v>
       </c>
       <c r="R15" s="5">
         <v>17</v>
@@ -5964,13 +5964,13 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.0149380808030668</v>
+        <v>-0.01692554605094188</v>
       </c>
       <c r="O16" s="5">
         <v>16</v>
       </c>
       <c r="P16" s="4">
-        <v>0.1584929467514735</v>
+        <v>0.1580197407400747</v>
       </c>
       <c r="Q16" s="4">
         <v>0.1116570568511746</v>
@@ -6023,7 +6023,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="4">
-        <v>1.180922108883423</v>
+        <v>1.181964072013784</v>
       </c>
       <c r="O17" s="5">
         <v>13</v>
@@ -6032,7 +6032,7 @@
         <v>0.2047023490117031</v>
       </c>
       <c r="Q17" s="4">
-        <v>0.04397129192556485</v>
+        <v>0.04389114091553709</v>
       </c>
       <c r="R17" s="5">
         <v>13</v>
@@ -6139,16 +6139,16 @@
         <v>0</v>
       </c>
       <c r="N19" s="4">
-        <v>0.1489480355294356</v>
+        <v>0.1186358553322862</v>
       </c>
       <c r="O19" s="5">
         <v>13</v>
       </c>
       <c r="P19" s="4">
-        <v>0.08823318948004293</v>
+        <v>0.08390287802330729</v>
       </c>
       <c r="Q19" s="4">
-        <v>0.09044070075387856</v>
+        <v>0.08810899458486705</v>
       </c>
       <c r="R19" s="5">
         <v>13</v>
@@ -6198,16 +6198,16 @@
         <v>0</v>
       </c>
       <c r="N20" s="4">
-        <v>0.07957832732282329</v>
+        <v>0.07482782693491785</v>
       </c>
       <c r="O20" s="5">
         <v>14</v>
       </c>
       <c r="P20" s="4">
-        <v>0.04517480854380407</v>
+        <v>0.04450661472519687</v>
       </c>
       <c r="Q20" s="4">
-        <v>0.04517480854380407</v>
+        <v>0.04450661472519687</v>
       </c>
       <c r="R20" s="5">
         <v>14</v>
@@ -6257,16 +6257,16 @@
         <v>0</v>
       </c>
       <c r="N21" s="4">
-        <v>0.05264414432257589</v>
+        <v>0.04370014243892939</v>
       </c>
       <c r="O21" s="5">
         <v>13</v>
       </c>
       <c r="P21" s="4">
-        <v>0.05165824591998355</v>
+        <v>0.0503805313651769</v>
       </c>
       <c r="Q21" s="4">
-        <v>0.0434719950242111</v>
+        <v>0.04278399487931522</v>
       </c>
       <c r="R21" s="5">
         <v>13</v>
@@ -6316,16 +6316,16 @@
         <v>0</v>
       </c>
       <c r="N22" s="4">
-        <v>0.1869292071216933</v>
+        <v>0.1554710544324962</v>
       </c>
       <c r="O22" s="5">
         <v>9</v>
       </c>
       <c r="P22" s="4">
-        <v>0.1942735111562074</v>
+        <v>0.1852854675307226</v>
       </c>
       <c r="Q22" s="4">
-        <v>0.09848120666924842</v>
+        <v>0.09498585637044875</v>
       </c>
       <c r="R22" s="5">
         <v>9</v>
@@ -6375,16 +6375,16 @@
         <v>0</v>
       </c>
       <c r="N23" s="4">
-        <v>0.4786900334925493</v>
+        <v>0.4773949806453643</v>
       </c>
       <c r="O23" s="5">
         <v>13</v>
       </c>
       <c r="P23" s="4">
-        <v>0.1017995470497619</v>
+        <v>0.1016145395001641</v>
       </c>
       <c r="Q23" s="4">
-        <v>0.1026953120724891</v>
+        <v>0.1025956926227056</v>
       </c>
       <c r="R23" s="5">
         <v>13</v>
@@ -6434,7 +6434,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="4">
-        <v>-0.520732554122167</v>
+        <v>-0.5206136923288511</v>
       </c>
       <c r="O24" s="5">
         <v>13</v>
@@ -6443,7 +6443,7 @@
         <v>0.2488025858490888</v>
       </c>
       <c r="Q24" s="4">
-        <v>0.09387965102144649</v>
+        <v>0.09387050780657603</v>
       </c>
       <c r="R24" s="5">
         <v>13</v>
@@ -6493,16 +6493,16 @@
         <v>0</v>
       </c>
       <c r="N25" s="4">
-        <v>-0.2775162165007828</v>
+        <v>-0.2567339168306972</v>
       </c>
       <c r="O25" s="5">
         <v>10</v>
       </c>
       <c r="P25" s="4">
-        <v>0.2410532493021979</v>
+        <v>0.2440971581404889</v>
       </c>
       <c r="Q25" s="4">
-        <v>0.1012402725651123</v>
+        <v>0.09718882507068542</v>
       </c>
       <c r="R25" s="5">
         <v>10</v>
@@ -6552,16 +6552,16 @@
         <v>0</v>
       </c>
       <c r="N26" s="4">
-        <v>-0.3223649731515908</v>
+        <v>-0.3135681359313764</v>
       </c>
       <c r="O26" s="5">
         <v>11</v>
       </c>
       <c r="P26" s="4">
-        <v>0.1283756606642653</v>
+        <v>0.1296323516957245</v>
       </c>
       <c r="Q26" s="4">
-        <v>0.1006333420728665</v>
+        <v>0.09983362959830154</v>
       </c>
       <c r="R26" s="5">
         <v>11</v>
@@ -6611,16 +6611,16 @@
         <v>0</v>
       </c>
       <c r="N27" s="4">
-        <v>-0.0372191251231021</v>
+        <v>0.01290435581294958</v>
       </c>
       <c r="O27" s="5">
         <v>13</v>
       </c>
       <c r="P27" s="4">
-        <v>0.126732853218797</v>
+        <v>0.1231505976581789</v>
       </c>
       <c r="Q27" s="4">
-        <v>0.1351326264744964</v>
+        <v>0.1274191604141345</v>
       </c>
       <c r="R27" s="5">
         <v>13</v>
@@ -6670,16 +6670,16 @@
         <v>0</v>
       </c>
       <c r="N28" s="4">
-        <v>-0.08901346712976631</v>
+        <v>-0.06944432911542719</v>
       </c>
       <c r="O28" s="5">
         <v>14</v>
       </c>
       <c r="P28" s="4">
-        <v>0.08997741099261992</v>
+        <v>0.0892676323292879</v>
       </c>
       <c r="Q28" s="4">
-        <v>0.08997741099261992</v>
+        <v>0.0892676323292879</v>
       </c>
       <c r="R28" s="5">
         <v>14</v>
@@ -6729,16 +6729,16 @@
         <v>0</v>
       </c>
       <c r="N29" s="4">
-        <v>-0.1764521187087404</v>
+        <v>-0.1865588162600318</v>
       </c>
       <c r="O29" s="5">
         <v>13</v>
       </c>
       <c r="P29" s="4">
-        <v>0.09543357729988568</v>
+        <v>0.09398976336398691</v>
       </c>
       <c r="Q29" s="4">
-        <v>0.08783014728304168</v>
+        <v>0.08705270900986542</v>
       </c>
       <c r="R29" s="5">
         <v>13</v>
@@ -6845,16 +6845,16 @@
         <v>0</v>
       </c>
       <c r="N31" s="4">
-        <v>-0.1068464936781102</v>
+        <v>-0.0554315042691087</v>
       </c>
       <c r="O31" s="5">
         <v>9</v>
       </c>
       <c r="P31" s="4">
-        <v>0.2217058846953399</v>
+        <v>0.2363958816693404</v>
       </c>
       <c r="Q31" s="4">
-        <v>0.1392558921496398</v>
+        <v>0.1335431155486396</v>
       </c>
       <c r="R31" s="5">
         <v>9</v>
@@ -6904,16 +6904,16 @@
         <v>0</v>
       </c>
       <c r="N32" s="4">
-        <v>0.1063753162010561</v>
+        <v>0.1920462308923447</v>
       </c>
       <c r="O32" s="5">
         <v>13</v>
       </c>
       <c r="P32" s="4">
-        <v>0.141958135736912</v>
+        <v>0.1340257006756487</v>
       </c>
       <c r="Q32" s="4">
-        <v>0.1484065949803834</v>
+        <v>0.1332739022458469</v>
       </c>
       <c r="R32" s="5">
         <v>13</v>
@@ -7160,13 +7160,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.3078485543727761</v>
+        <v>0.3072211044997065</v>
       </c>
       <c r="I3" s="4">
-        <v>0.1656898738737071</v>
+        <v>0.1634565998612629</v>
       </c>
       <c r="J3" s="4">
-        <v>0.2812898203803343</v>
+        <v>0.2748229945996697</v>
       </c>
       <c r="K3" s="4">
         <v>86.82263611764408</v>
@@ -7210,13 +7210,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.5393429459996723</v>
+        <v>0.5435779322445913</v>
       </c>
       <c r="I4" s="4">
-        <v>0.1863864259509189</v>
+        <v>0.1817699486939461</v>
       </c>
       <c r="J4" s="4">
-        <v>0.2515686097914874</v>
+        <v>0.2592818069719915</v>
       </c>
       <c r="K4" s="4">
         <v>77.50031611157472</v>
@@ -7260,13 +7260,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.1543712499026453</v>
+        <v>0.1544232937612892</v>
       </c>
       <c r="I5" s="4">
-        <v>0.06780238944433035</v>
+        <v>0.06555114815299169</v>
       </c>
       <c r="J5" s="4">
-        <v>0.09536785823398788</v>
+        <v>0.09330207163746967</v>
       </c>
       <c r="K5" s="4">
         <v>85.37459221606881</v>
@@ -7310,13 +7310,13 @@
         <v>0.1858736059479554</v>
       </c>
       <c r="H6" s="4">
-        <v>0.3753315547362477</v>
+        <v>0.3722515093663683</v>
       </c>
       <c r="I6" s="4">
-        <v>0.126841980580315</v>
+        <v>0.1244420125454243</v>
       </c>
       <c r="J6" s="4">
-        <v>0.2057683678771257</v>
+        <v>0.2050835917814238</v>
       </c>
       <c r="K6" s="4">
         <v>85.09495991705236</v>
@@ -7360,13 +7360,13 @@
         <v>0.1858736059479554</v>
       </c>
       <c r="H7" s="4">
-        <v>0.2569761379622667</v>
+        <v>0.2578555046497535</v>
       </c>
       <c r="I7" s="4">
-        <v>0.08609780316751174</v>
+        <v>0.0849195533592861</v>
       </c>
       <c r="J7" s="4">
-        <v>0.1048066987502159</v>
+        <v>0.1011459273998556</v>
       </c>
       <c r="K7" s="4">
         <v>87.97669625470986</v>
@@ -7410,13 +7410,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.2762904005901693</v>
+        <v>0.2810712261904636</v>
       </c>
       <c r="I8" s="4">
-        <v>0.1147723366840288</v>
+        <v>0.1112331209554729</v>
       </c>
       <c r="J8" s="4">
-        <v>0.1500325461315589</v>
+        <v>0.1519759855257864</v>
       </c>
       <c r="K8" s="4">
         <v>85.41676150013883</v>
@@ -7460,13 +7460,13 @@
         <v>1.4</v>
       </c>
       <c r="H9" s="4">
-        <v>0.711093367779626</v>
+        <v>0.7018475482038382</v>
       </c>
       <c r="I9" s="4">
-        <v>0.1739747498251698</v>
+        <v>0.162066044043914</v>
       </c>
       <c r="J9" s="4">
-        <v>0.3065426003947408</v>
+        <v>0.290703576989432</v>
       </c>
       <c r="K9" s="4">
         <v>78.20047619047621</v>
@@ -7510,13 +7510,13 @@
         <v>0.1858736059479554</v>
       </c>
       <c r="H10" s="4">
-        <v>0.1920051133602973</v>
+        <v>0.1911752613475564</v>
       </c>
       <c r="I10" s="4">
-        <v>0.09871716931175874</v>
+        <v>0.09702375883829645</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1375397021190568</v>
+        <v>0.1360906684546041</v>
       </c>
       <c r="K10" s="4">
         <v>85.42112383987029</v>
@@ -8597,16 +8597,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.229064213620596</v>
+        <v>0.1941780407250846</v>
       </c>
       <c r="O3" s="5">
         <v>32</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1630839516983049</v>
+        <v>0.1612993494726584</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1630839516983049</v>
+        <v>0.1612993494726584</v>
       </c>
       <c r="R3" s="5">
         <v>32</v>
@@ -8656,16 +8656,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1664310456470741</v>
+        <v>-0.2022936060058669</v>
       </c>
       <c r="O4" s="5">
         <v>25</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3335177650406291</v>
+        <v>0.3309561535864297</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.294523891725097</v>
+        <v>0.2930893893107452</v>
       </c>
       <c r="R4" s="5">
         <v>25</v>
@@ -8715,16 +8715,16 @@
         <v>14</v>
       </c>
       <c r="N5" s="4">
-        <v>2.270082883373705</v>
+        <v>2.24630407939452</v>
       </c>
       <c r="O5" s="5">
         <v>15</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4691763334562303</v>
+        <v>0.4618178405301335</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1211654205986161</v>
+        <v>0.1195801670000037</v>
       </c>
       <c r="R5" s="5">
         <v>15</v>
@@ -8774,16 +8774,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.1555902242268827</v>
+        <v>0.1770776060644579</v>
       </c>
       <c r="O6" s="5">
         <v>18</v>
       </c>
       <c r="P6" s="4">
-        <v>0.258992013899893</v>
+        <v>0.2607915249807002</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1277031375376148</v>
+        <v>0.1262213368256274</v>
       </c>
       <c r="R6" s="5">
         <v>18</v>
@@ -8833,16 +8833,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.07467097139159116</v>
+        <v>-0.09433918354002913</v>
       </c>
       <c r="O7" s="5">
         <v>11</v>
       </c>
       <c r="P7" s="4">
-        <v>0.9913029108519379</v>
+        <v>0.9810005140122797</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.08696811056107955</v>
+        <v>0.08518009127485791</v>
       </c>
       <c r="R7" s="5">
         <v>11</v>
@@ -8892,16 +8892,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.3116606251116139</v>
+        <v>0.3500431252734586</v>
       </c>
       <c r="O8" s="5">
         <v>21</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1784902363079314</v>
+        <v>0.1766624982049864</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1784902363079314</v>
+        <v>0.1766624982049864</v>
       </c>
       <c r="R8" s="5">
         <v>21</v>
@@ -8951,16 +8951,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.1593047483840436</v>
+        <v>0.1628794954101807</v>
       </c>
       <c r="O9" s="5">
         <v>19</v>
       </c>
       <c r="P9" s="4">
-        <v>0.1662142565315647</v>
+        <v>0.166044030482701</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1677877704510064</v>
+        <v>0.1675996258706834</v>
       </c>
       <c r="R9" s="5">
         <v>19</v>
@@ -9010,13 +9010,13 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.256523421685543</v>
+        <v>0.2606431890722689</v>
       </c>
       <c r="O10" s="5">
         <v>20</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1623437009614908</v>
+        <v>0.1625398803608587</v>
       </c>
       <c r="Q10" s="4">
         <v>0.155620261785154</v>
@@ -9069,16 +9069,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>0.5826738518139649</v>
+        <v>0.6073227857885826</v>
       </c>
       <c r="O11" s="5">
         <v>18</v>
       </c>
       <c r="P11" s="4">
-        <v>0.3415591254604886</v>
+        <v>0.3432047497510863</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1079379254258836</v>
+        <v>0.1057496647691446</v>
       </c>
       <c r="R11" s="5">
         <v>18</v>
@@ -9128,16 +9128,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.717148745096362</v>
+        <v>0.7107264960156385</v>
       </c>
       <c r="O12" s="5">
         <v>15</v>
       </c>
       <c r="P12" s="4">
-        <v>0.4707592942063533</v>
+        <v>0.4692301872823715</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.09142721692570101</v>
+        <v>0.09099906698698608</v>
       </c>
       <c r="R12" s="5">
         <v>15</v>
@@ -9187,16 +9187,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.5190475816683081</v>
+        <v>0.510332777446294</v>
       </c>
       <c r="O13" s="5">
         <v>12</v>
       </c>
       <c r="P13" s="4">
-        <v>0.9840983359599801</v>
+        <v>0.9796414500576628</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.08321221139756733</v>
+        <v>0.08194876423502251</v>
       </c>
       <c r="R13" s="5">
         <v>12</v>
@@ -9246,16 +9246,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.4797019021047247</v>
+        <v>0.4872899005859495</v>
       </c>
       <c r="O14" s="5">
         <v>21</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1953647066510754</v>
+        <v>0.1950033733900647</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1953647066510754</v>
+        <v>0.1950033733900647</v>
       </c>
       <c r="R14" s="5">
         <v>21</v>
@@ -9305,16 +9305,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>0.358202100462062</v>
+        <v>0.3652034387402239</v>
       </c>
       <c r="O15" s="5">
         <v>19</v>
       </c>
       <c r="P15" s="4">
-        <v>0.1937206697124658</v>
+        <v>0.193387272651601</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.1948807337817055</v>
+        <v>0.1945122422933812</v>
       </c>
       <c r="R15" s="5">
         <v>19</v>
@@ -9364,13 +9364,13 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.01348255996288685</v>
+        <v>-0.01304083904783226</v>
       </c>
       <c r="O16" s="5">
         <v>20</v>
       </c>
       <c r="P16" s="4">
-        <v>0.1977509179779149</v>
+        <v>0.1977298836486266</v>
       </c>
       <c r="Q16" s="4">
         <v>0.2065754555322286</v>
@@ -9423,7 +9423,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="4">
-        <v>1.355608132188706</v>
+        <v>1.32535374050903</v>
       </c>
       <c r="O17" s="5">
         <v>10</v>
@@ -9482,13 +9482,13 @@
         <v>0</v>
       </c>
       <c r="N18" s="4">
-        <v>-0.7236021407470711</v>
+        <v>-0.6383139023876936</v>
       </c>
       <c r="O18" s="5">
         <v>6</v>
       </c>
       <c r="P18" s="4">
-        <v>0.2905786073451422</v>
+        <v>0.3060565252134455</v>
       </c>
       <c r="Q18" s="4">
         <v>0.2365099459114598</v>
@@ -9541,16 +9541,16 @@
         <v>0</v>
       </c>
       <c r="N19" s="4">
-        <v>-0.1113454884988922</v>
+        <v>-0.1189152194921945</v>
       </c>
       <c r="O19" s="5">
         <v>14</v>
       </c>
       <c r="P19" s="4">
-        <v>0.01679125488998735</v>
+        <v>0.01506622669084834</v>
       </c>
       <c r="Q19" s="4">
-        <v>0.01679125488998735</v>
+        <v>0.01506622669084834</v>
       </c>
       <c r="R19" s="5">
         <v>14</v>
@@ -9600,16 +9600,16 @@
         <v>0</v>
       </c>
       <c r="N20" s="4">
-        <v>-0.1618496993045499</v>
+        <v>-0.1453916974707141</v>
       </c>
       <c r="O20" s="5">
         <v>14</v>
       </c>
       <c r="P20" s="4">
-        <v>0.04944222401516118</v>
+        <v>0.04817850919433146</v>
       </c>
       <c r="Q20" s="4">
-        <v>0.04944222401516118</v>
+        <v>0.04817850919433146</v>
       </c>
       <c r="R20" s="5">
         <v>14</v>
@@ -9659,16 +9659,16 @@
         <v>0</v>
       </c>
       <c r="N21" s="4">
-        <v>0.002073883821606633</v>
+        <v>0.003523629941398099</v>
       </c>
       <c r="O21" s="5">
         <v>12</v>
       </c>
       <c r="P21" s="4">
-        <v>0.05471452780133949</v>
+        <v>0.05480335778459887</v>
       </c>
       <c r="Q21" s="4">
-        <v>0.02239981653428952</v>
+        <v>0.02226182716146023</v>
       </c>
       <c r="R21" s="5">
         <v>12</v>
@@ -9718,16 +9718,16 @@
         <v>0</v>
       </c>
       <c r="N22" s="4">
-        <v>-0.04329375208718292</v>
+        <v>-0.04569189296873333</v>
       </c>
       <c r="O22" s="5">
         <v>11</v>
       </c>
       <c r="P22" s="4">
-        <v>0.2910917737179733</v>
+        <v>0.2904065906089589</v>
       </c>
       <c r="Q22" s="4">
-        <v>0.1568228140938131</v>
+        <v>0.1566048012863994</v>
       </c>
       <c r="R22" s="5">
         <v>11</v>
@@ -9777,16 +9777,16 @@
         <v>8</v>
       </c>
       <c r="N23" s="4">
-        <v>2.124175707935905</v>
+        <v>2.089788660224599</v>
       </c>
       <c r="O23" s="5">
         <v>11</v>
       </c>
       <c r="P23" s="4">
-        <v>0.1188144904303832</v>
+        <v>0.1213967084758687</v>
       </c>
       <c r="Q23" s="4">
-        <v>0.1448763278033001</v>
+        <v>0.1417502325568178</v>
       </c>
       <c r="R23" s="5">
         <v>11</v>
@@ -9836,16 +9836,16 @@
         <v>0</v>
       </c>
       <c r="N24" s="4">
-        <v>0.1949385573956797</v>
+        <v>0.1542269996045036</v>
       </c>
       <c r="O24" s="5">
         <v>11</v>
       </c>
       <c r="P24" s="4">
-        <v>0.5494657069328281</v>
+        <v>0.5341276079687499</v>
       </c>
       <c r="Q24" s="4">
-        <v>0.2084821172314011</v>
+        <v>0.2000640524928951</v>
       </c>
       <c r="R24" s="5">
         <v>11</v>
@@ -9895,16 +9895,16 @@
         <v>0</v>
       </c>
       <c r="N25" s="4">
-        <v>0.1102836733548713</v>
+        <v>0.1037650668554591</v>
       </c>
       <c r="O25" s="5">
         <v>13</v>
       </c>
       <c r="P25" s="4">
-        <v>0.2492492508329219</v>
+        <v>0.2483180213330058</v>
       </c>
       <c r="Q25" s="4">
-        <v>0.2124074187797017</v>
+        <v>0.2119059875105161</v>
       </c>
       <c r="R25" s="5">
         <v>13</v>
@@ -9954,13 +9954,13 @@
         <v>0</v>
       </c>
       <c r="N26" s="4">
-        <v>-0.1812139758512288</v>
+        <v>-0.2112045818798833</v>
       </c>
       <c r="O26" s="5">
         <v>12</v>
       </c>
       <c r="P26" s="4">
-        <v>0.2468895790922576</v>
+        <v>0.2426052068024498</v>
       </c>
       <c r="Q26" s="4">
         <v>0.2023179826171813</v>
@@ -10013,16 +10013,16 @@
         <v>0</v>
       </c>
       <c r="N27" s="4">
-        <v>0.5794813521798261</v>
+        <v>0.613521315458982</v>
       </c>
       <c r="O27" s="5">
         <v>14</v>
       </c>
       <c r="P27" s="4">
-        <v>0.1576862266884486</v>
+        <v>0.1543606864711141</v>
       </c>
       <c r="Q27" s="4">
-        <v>0.1576862266884486</v>
+        <v>0.1543606864711141</v>
       </c>
       <c r="R27" s="5">
         <v>14</v>
@@ -10072,16 +10072,16 @@
         <v>0</v>
       </c>
       <c r="N28" s="4">
-        <v>0.5845337045131122</v>
+        <v>0.6047604787695349</v>
       </c>
       <c r="O28" s="5">
         <v>14</v>
       </c>
       <c r="P28" s="4">
-        <v>0.1389594867376894</v>
+        <v>0.1355751531612798</v>
       </c>
       <c r="Q28" s="4">
-        <v>0.1389594867376894</v>
+        <v>0.1355751531612798</v>
       </c>
       <c r="R28" s="5">
         <v>14</v>
@@ -10131,16 +10131,16 @@
         <v>0</v>
       </c>
       <c r="N29" s="4">
-        <v>0.1403617215995373</v>
+        <v>0.1645662400976704</v>
       </c>
       <c r="O29" s="5">
         <v>12</v>
       </c>
       <c r="P29" s="4">
-        <v>0.1747554763227752</v>
+        <v>0.173309100932268</v>
       </c>
       <c r="Q29" s="4">
-        <v>0.1716749280637586</v>
+        <v>0.1659534036918112</v>
       </c>
       <c r="R29" s="5">
         <v>12</v>
@@ -10190,16 +10190,16 @@
         <v>0</v>
       </c>
       <c r="N30" s="4">
-        <v>-0.3212834374275673</v>
+        <v>-0.1248296734570289</v>
       </c>
       <c r="O30" s="5">
         <v>6</v>
       </c>
       <c r="P30" s="4">
-        <v>0.378941472488488</v>
+        <v>0.424437126349395</v>
       </c>
       <c r="Q30" s="4">
-        <v>0.2915779362331818</v>
+        <v>0.2373785848185198</v>
       </c>
       <c r="R30" s="5">
         <v>6</v>
@@ -10249,16 +10249,16 @@
         <v>0</v>
       </c>
       <c r="N31" s="4">
-        <v>0.1300669264399801</v>
+        <v>0.1025982535156231</v>
       </c>
       <c r="O31" s="5">
         <v>11</v>
       </c>
       <c r="P31" s="4">
-        <v>0.3222446704365325</v>
+        <v>0.3143964781724305</v>
       </c>
       <c r="Q31" s="4">
-        <v>0.2159143545130074</v>
+        <v>0.213417202428975</v>
       </c>
       <c r="R31" s="5">
         <v>11</v>
@@ -10308,16 +10308,16 @@
         <v>0</v>
       </c>
       <c r="N32" s="4">
-        <v>0.476684286711653</v>
+        <v>0.5063873520312825</v>
       </c>
       <c r="O32" s="5">
         <v>11</v>
       </c>
       <c r="P32" s="4">
-        <v>0.1688134970880636</v>
+        <v>0.1645702020424023</v>
       </c>
       <c r="Q32" s="4">
-        <v>0.2028391271526359</v>
+        <v>0.2001388484872151</v>
       </c>
       <c r="R32" s="5">
         <v>11</v>
@@ -10604,16 +10604,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2542958372534088</v>
+        <v>0.2908717756249928</v>
       </c>
       <c r="O3" s="5">
         <v>31</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2018259275222016</v>
+        <v>0.1965029323831944</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2049451692740364</v>
+        <v>0.2006303335941445</v>
       </c>
       <c r="R3" s="5">
         <v>31</v>
@@ -10663,16 +10663,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.7757832149414023</v>
+        <v>0.8124958283593742</v>
       </c>
       <c r="O4" s="5">
         <v>19</v>
       </c>
       <c r="P4" s="4">
-        <v>0.408210197378279</v>
+        <v>0.4183607727926204</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1111077818791114</v>
+        <v>0.1091755390676392</v>
       </c>
       <c r="R4" s="5">
         <v>19</v>
@@ -10722,16 +10722,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>1.286707093211267</v>
+        <v>1.324551948144517</v>
       </c>
       <c r="O5" s="5">
         <v>12</v>
       </c>
       <c r="P5" s="4">
-        <v>0.6882334684533887</v>
+        <v>0.7003763115317987</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1105925024842694</v>
+        <v>0.1034588366715496</v>
       </c>
       <c r="R5" s="5">
         <v>12</v>
@@ -10781,16 +10781,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>1.231615824993485</v>
+        <v>1.244030217636706</v>
       </c>
       <c r="O6" s="5">
         <v>18</v>
       </c>
       <c r="P6" s="4">
-        <v>0.3265768014905739</v>
+        <v>0.3274137131119767</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.09709032356409038</v>
+        <v>0.0959976550151901</v>
       </c>
       <c r="R6" s="5">
         <v>18</v>
@@ -10840,13 +10840,13 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>1.357496362941898</v>
+        <v>1.352711992739259</v>
       </c>
       <c r="O7" s="5">
         <v>8</v>
       </c>
       <c r="P7" s="4">
-        <v>1.203423926597491</v>
+        <v>1.200462173614905</v>
       </c>
       <c r="Q7" s="4">
         <v>0.1023545680932649</v>
@@ -10899,13 +10899,13 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.5544115629915451</v>
+        <v>0.538381819921895</v>
       </c>
       <c r="O8" s="5">
         <v>18</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1909040157319592</v>
+        <v>0.1886140524362949</v>
       </c>
       <c r="Q8" s="4">
         <v>0.1403211909928391</v>
@@ -10958,16 +10958,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.4243064638012655</v>
+        <v>0.3726014722704889</v>
       </c>
       <c r="O9" s="5">
         <v>16</v>
       </c>
       <c r="P9" s="4">
-        <v>0.1863666192093332</v>
+        <v>0.172072156325564</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.122349626699525</v>
+        <v>0.1161250429052707</v>
       </c>
       <c r="R9" s="5">
         <v>16</v>
@@ -11017,13 +11017,13 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.4381831201718711</v>
+        <v>0.4460163264453172</v>
       </c>
       <c r="O10" s="5">
         <v>20</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1220382298816883</v>
+        <v>0.1224112397042334</v>
       </c>
       <c r="Q10" s="4">
         <v>0.1167926354374941</v>
@@ -11076,16 +11076,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>0.7775652079589845</v>
+        <v>0.8738719156152257</v>
       </c>
       <c r="O11" s="5">
         <v>18</v>
       </c>
       <c r="P11" s="4">
-        <v>0.3877135006849852</v>
+        <v>0.3927348774186145</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1469876780522983</v>
+        <v>0.1367948329654922</v>
       </c>
       <c r="R11" s="5">
         <v>18</v>
@@ -11135,16 +11135,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.7241646570483434</v>
+        <v>0.8209159473046697</v>
       </c>
       <c r="O12" s="5">
         <v>12</v>
       </c>
       <c r="P12" s="4">
-        <v>0.6476642888398667</v>
+        <v>0.68006150767903</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1737394166906781</v>
+        <v>0.157871081966969</v>
       </c>
       <c r="R12" s="5">
         <v>12</v>
@@ -11194,16 +11194,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>1.223855306289078</v>
+        <v>1.29100753191409</v>
       </c>
       <c r="O13" s="5">
         <v>8</v>
       </c>
       <c r="P13" s="4">
-        <v>1.268889902150305</v>
+        <v>1.306676306878738</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1755063299121113</v>
+        <v>0.1655732756836024</v>
       </c>
       <c r="R13" s="5">
         <v>8</v>
@@ -11253,16 +11253,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.3195168803073614</v>
+        <v>0.2908786166211144</v>
       </c>
       <c r="O14" s="5">
         <v>19</v>
       </c>
       <c r="P14" s="4">
-        <v>0.2550906696053598</v>
+        <v>0.2489161312890617</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.2269589570273518</v>
+        <v>0.2231490213815747</v>
       </c>
       <c r="R14" s="5">
         <v>19</v>
@@ -11312,13 +11312,13 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>0.2604624207226518</v>
+        <v>0.236622159921879</v>
       </c>
       <c r="O15" s="5">
         <v>16</v>
       </c>
       <c r="P15" s="4">
-        <v>0.2742040379473571</v>
+        <v>0.2685277853757445</v>
       </c>
       <c r="Q15" s="4">
         <v>0.2238384693164033</v>
@@ -11371,16 +11371,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>0.1512086021464882</v>
+        <v>0.1180976950195287</v>
       </c>
       <c r="O16" s="5">
         <v>20</v>
       </c>
       <c r="P16" s="4">
-        <v>0.1973595722420926</v>
+        <v>0.1928125278050587</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.2011669363044922</v>
+        <v>0.1980480850019546</v>
       </c>
       <c r="R16" s="5">
         <v>20</v>
@@ -11428,13 +11428,13 @@
         <v>6</v>
       </c>
       <c r="N17" s="4">
-        <v>3.300654319518211</v>
+        <v>3.309615795195285</v>
       </c>
       <c r="O17" s="5">
         <v>6</v>
       </c>
       <c r="P17" s="4">
-        <v>1.559369232857145</v>
+        <v>1.563209865290176</v>
       </c>
       <c r="Q17" s="4">
         <v>0.1094455273046909</v>
@@ -11715,16 +11715,16 @@
         <v>0</v>
       </c>
       <c r="N22" s="4">
-        <v>0.6155353946679781</v>
+        <v>0.6236142017968973</v>
       </c>
       <c r="O22" s="5">
         <v>5</v>
       </c>
       <c r="P22" s="4">
-        <v>0.6323580449602469</v>
+        <v>0.6369745061767722</v>
       </c>
       <c r="Q22" s="4">
-        <v>0.05894998429686667</v>
+        <v>0.05733422287108283</v>
       </c>
       <c r="R22" s="5">
         <v>5</v>
@@ -11831,16 +11831,16 @@
         <v>0</v>
       </c>
       <c r="N24" s="4">
-        <v>0.6212846044999992</v>
+        <v>0.6816131727343588</v>
       </c>
       <c r="O24" s="5">
         <v>5</v>
       </c>
       <c r="P24" s="4">
-        <v>2.077076659231448</v>
+        <v>2.095554860367603</v>
       </c>
       <c r="Q24" s="4">
-        <v>0.1908543097374922</v>
+        <v>0.158133277390624</v>
       </c>
       <c r="R24" s="5">
         <v>5</v>
@@ -11890,16 +11890,16 @@
         <v>0</v>
       </c>
       <c r="N25" s="4">
-        <v>0.1526104405208362</v>
+        <v>0.2613745108593832</v>
       </c>
       <c r="O25" s="5">
         <v>9</v>
       </c>
       <c r="P25" s="4">
-        <v>0.5165742999739582</v>
+        <v>0.5462254218638398</v>
       </c>
       <c r="Q25" s="4">
-        <v>0.1961184988541681</v>
+        <v>0.1818179827170133</v>
       </c>
       <c r="R25" s="5">
         <v>9</v>
@@ -11949,16 +11949,16 @@
         <v>0</v>
       </c>
       <c r="N26" s="4">
-        <v>0.01550914008203677</v>
+        <v>0.0624168588281151</v>
       </c>
       <c r="O26" s="5">
         <v>10</v>
       </c>
       <c r="P26" s="4">
-        <v>0.426047344891735</v>
+        <v>0.4332737297014425</v>
       </c>
       <c r="Q26" s="4">
-        <v>0.1801632792609314</v>
+        <v>0.1715171304960904</v>
       </c>
       <c r="R26" s="5">
         <v>10</v>
@@ -12236,16 +12236,16 @@
         <v>0</v>
       </c>
       <c r="N31" s="4">
-        <v>0.2787691290156203</v>
+        <v>0.299553423359356</v>
       </c>
       <c r="O31" s="5">
         <v>5</v>
       </c>
       <c r="P31" s="4">
-        <v>0.7258848717756693</v>
+        <v>0.7377616114006612</v>
       </c>
       <c r="Q31" s="4">
-        <v>0.1163022709000006</v>
+        <v>0.1121454120312535</v>
       </c>
       <c r="R31" s="5">
         <v>5</v>
@@ -12585,16 +12585,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0828567195719998</v>
+        <v>-0.07885387256307297</v>
       </c>
       <c r="O3" s="5">
         <v>32</v>
       </c>
       <c r="P3" s="4">
-        <v>0.07784893780608293</v>
+        <v>0.07741447428181747</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.07784893780608293</v>
+        <v>0.07741447428181747</v>
       </c>
       <c r="R3" s="5">
         <v>32</v>
@@ -12644,16 +12644,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1478155297779961</v>
+        <v>-0.1169800925488289</v>
       </c>
       <c r="O4" s="5">
         <v>19</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1013264255158858</v>
+        <v>0.1083505489360854</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.0827484904509298</v>
+        <v>0.08112557270202626</v>
       </c>
       <c r="R4" s="5">
         <v>19</v>
@@ -12703,16 +12703,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.6109096195608509</v>
+        <v>0.5987012995156675</v>
       </c>
       <c r="O5" s="5">
         <v>18</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1669726472107412</v>
+        <v>0.1647505767713749</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.06803329908355327</v>
+        <v>0.06747560357848986</v>
       </c>
       <c r="R5" s="5">
         <v>18</v>
@@ -12762,16 +12762,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.4881890826347345</v>
+        <v>0.476200056913143</v>
       </c>
       <c r="O6" s="5">
         <v>19</v>
       </c>
       <c r="P6" s="4">
-        <v>0.08722665660845833</v>
+        <v>0.08546854600524918</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.06338731226521092</v>
+        <v>0.06270614009551573</v>
       </c>
       <c r="R6" s="5">
         <v>19</v>
@@ -12821,16 +12821,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.3497663743117272</v>
+        <v>0.3691263702777405</v>
       </c>
       <c r="O7" s="5">
         <v>15</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2366072727087344</v>
+        <v>0.2393729864181649</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.06475454858968988</v>
+        <v>0.06346388219195566</v>
       </c>
       <c r="R7" s="5">
         <v>15</v>
@@ -12880,16 +12880,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.2536430795397654</v>
+        <v>-0.2798061782173988</v>
       </c>
       <c r="O8" s="5">
         <v>19</v>
       </c>
       <c r="P8" s="4">
-        <v>0.06867750178353378</v>
+        <v>0.06164208903409948</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.05958793471920375</v>
+        <v>0.05456596259379042</v>
       </c>
       <c r="R8" s="5">
         <v>19</v>
@@ -12939,16 +12939,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.2910196245378546</v>
+        <v>-0.3159355725328226</v>
       </c>
       <c r="O9" s="5">
         <v>17</v>
       </c>
       <c r="P9" s="4">
-        <v>0.086507161048286</v>
+        <v>0.07970282463774868</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.06559939339967104</v>
+        <v>0.06305661265605857</v>
       </c>
       <c r="R9" s="5">
         <v>17</v>
@@ -12998,16 +12998,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.4016023564765844</v>
+        <v>-0.4126479035662101</v>
       </c>
       <c r="O10" s="5">
         <v>19</v>
       </c>
       <c r="P10" s="4">
-        <v>0.06198278054488481</v>
+        <v>0.06038796793926947</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.04810746567545768</v>
+        <v>0.04750746722605395</v>
       </c>
       <c r="R10" s="5">
         <v>19</v>
@@ -13057,16 +13057,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>0.1302990629355634</v>
+        <v>0.1423045632896276</v>
       </c>
       <c r="O11" s="5">
         <v>19</v>
       </c>
       <c r="P11" s="4">
-        <v>0.1111102483703194</v>
+        <v>0.1112333215521887</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.09548280311178371</v>
+        <v>0.0943550944860536</v>
       </c>
       <c r="R11" s="5">
         <v>19</v>
@@ -13116,16 +13116,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.0121868648694677</v>
+        <v>0.01525081157653574</v>
       </c>
       <c r="O12" s="5">
         <v>18</v>
       </c>
       <c r="P12" s="4">
-        <v>0.1509355172779154</v>
+        <v>0.1511877155484706</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.07362179160003067</v>
+        <v>0.07340536513116705</v>
       </c>
       <c r="R12" s="5">
         <v>18</v>
@@ -13175,13 +13175,13 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.4338050584568691</v>
+        <v>-0.4340278524340135</v>
       </c>
       <c r="O13" s="5">
         <v>16</v>
       </c>
       <c r="P13" s="4">
-        <v>0.3476323435423175</v>
+        <v>0.3476217343053106</v>
       </c>
       <c r="Q13" s="4">
         <v>0.107188326949526</v>
@@ -13234,16 +13234,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.1662154074493452</v>
+        <v>-0.2215527889987357</v>
       </c>
       <c r="O14" s="5">
         <v>19</v>
       </c>
       <c r="P14" s="4">
-        <v>0.07873787821922053</v>
+        <v>0.07364547421366432</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.08292763230311485</v>
+        <v>0.07680486807563482</v>
       </c>
       <c r="R14" s="5">
         <v>19</v>
@@ -13293,16 +13293,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>-0.09796887514449495</v>
+        <v>-0.1285769843078413</v>
       </c>
       <c r="O15" s="5">
         <v>17</v>
       </c>
       <c r="P15" s="4">
-        <v>0.09082263869842654</v>
+        <v>0.08497953652542919</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.08124905125168762</v>
+        <v>0.07763205552779047</v>
       </c>
       <c r="R15" s="5">
         <v>17</v>
@@ -13352,16 +13352,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.08436534400062842</v>
+        <v>-0.1095988431620754</v>
       </c>
       <c r="O16" s="5">
         <v>19</v>
       </c>
       <c r="P16" s="4">
-        <v>0.08301118238727993</v>
+        <v>0.07815307170020398</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.07929727292102617</v>
+        <v>0.07658393996809452</v>
       </c>
       <c r="R16" s="5">
         <v>19</v>
@@ -13411,16 +13411,16 @@
         <v>0</v>
       </c>
       <c r="N17" s="4">
-        <v>1.55951718513155</v>
+        <v>1.583955030384203</v>
       </c>
       <c r="O17" s="5">
         <v>11</v>
       </c>
       <c r="P17" s="4">
-        <v>0.4879276046334107</v>
+        <v>0.4912168991976549</v>
       </c>
       <c r="Q17" s="4">
-        <v>0.04846650517822297</v>
+        <v>0.04598801319108309</v>
       </c>
       <c r="R17" s="5">
         <v>11</v>
@@ -13470,16 +13470,16 @@
         <v>0</v>
       </c>
       <c r="N18" s="4">
-        <v>-0.05043218440323471</v>
+        <v>0.02718934997579936</v>
       </c>
       <c r="O18" s="5">
         <v>7</v>
       </c>
       <c r="P18" s="4">
-        <v>0.5024254973954905</v>
+        <v>0.5267550284651544</v>
       </c>
       <c r="Q18" s="4">
-        <v>0.1383322499726936</v>
+        <v>0.1093697777329875</v>
       </c>
       <c r="R18" s="5">
         <v>7</v>
@@ -13529,7 +13529,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="4">
-        <v>-0.03257469106529446</v>
+        <v>-0.03351290076003011</v>
       </c>
       <c r="O19" s="5">
         <v>14</v>
@@ -13588,16 +13588,16 @@
         <v>0</v>
       </c>
       <c r="N20" s="4">
-        <v>-0.04315150441546426</v>
+        <v>-0.04840461058414292</v>
       </c>
       <c r="O20" s="5">
         <v>14</v>
       </c>
       <c r="P20" s="4">
-        <v>0.02858319903979247</v>
+        <v>0.02791556459308302</v>
       </c>
       <c r="Q20" s="4">
-        <v>0.02858319903979247</v>
+        <v>0.02791556459308302</v>
       </c>
       <c r="R20" s="5">
         <v>14</v>
@@ -13647,16 +13647,16 @@
         <v>0</v>
       </c>
       <c r="N21" s="4">
-        <v>-0.05959671581517512</v>
+        <v>-0.06535392022838948</v>
       </c>
       <c r="O21" s="5">
         <v>14</v>
       </c>
       <c r="P21" s="4">
-        <v>0.02011727568600463</v>
+        <v>0.0199341842359522</v>
       </c>
       <c r="Q21" s="4">
-        <v>0.02011727568600463</v>
+        <v>0.0199341842359522</v>
       </c>
       <c r="R21" s="5">
         <v>14</v>
@@ -13706,16 +13706,16 @@
         <v>0</v>
       </c>
       <c r="N22" s="4">
-        <v>-0.05570254966487988</v>
+        <v>-0.06600229475009201</v>
       </c>
       <c r="O22" s="5">
         <v>9</v>
       </c>
       <c r="P22" s="4">
-        <v>0.1967373114161216</v>
+        <v>0.1923231349510307</v>
       </c>
       <c r="Q22" s="4">
-        <v>0.06541586975791101</v>
+        <v>0.06427145363733189</v>
       </c>
       <c r="R22" s="5">
         <v>9</v>
@@ -13765,16 +13765,16 @@
         <v>0</v>
       </c>
       <c r="N23" s="4">
-        <v>0.5015999331154598</v>
+        <v>0.5153732513461904</v>
       </c>
       <c r="O23" s="5">
         <v>12</v>
       </c>
       <c r="P23" s="4">
-        <v>0.06686955993537172</v>
+        <v>0.06703367581939647</v>
       </c>
       <c r="Q23" s="4">
-        <v>0.05330759929681941</v>
+        <v>0.05120351478972651</v>
       </c>
       <c r="R23" s="5">
         <v>12</v>
@@ -13824,16 +13824,16 @@
         <v>0</v>
       </c>
       <c r="N24" s="4">
-        <v>-0.6020297903648043</v>
+        <v>-0.6128477877479384</v>
       </c>
       <c r="O24" s="5">
         <v>10</v>
       </c>
       <c r="P24" s="4">
-        <v>0.641438076991979</v>
+        <v>0.6376071383976571</v>
       </c>
       <c r="Q24" s="4">
-        <v>0.06872069668164726</v>
+        <v>0.06768458160285036</v>
       </c>
       <c r="R24" s="5">
         <v>10</v>
@@ -13883,16 +13883,16 @@
         <v>0</v>
       </c>
       <c r="N25" s="4">
-        <v>-0.3696028533049305</v>
+        <v>-0.3742075784570886</v>
       </c>
       <c r="O25" s="5">
         <v>9</v>
       </c>
       <c r="P25" s="4">
-        <v>0.07134552049395131</v>
+        <v>0.06937206685731212</v>
       </c>
       <c r="Q25" s="4">
-        <v>0.03391747715422795</v>
+        <v>0.03340584102621039</v>
       </c>
       <c r="R25" s="5">
         <v>9</v>
@@ -13942,13 +13942,13 @@
         <v>0</v>
       </c>
       <c r="N26" s="4">
-        <v>-0.4553502858396882</v>
+        <v>-0.4550363087606968</v>
       </c>
       <c r="O26" s="5">
         <v>10</v>
       </c>
       <c r="P26" s="4">
-        <v>0.1221123620713091</v>
+        <v>0.1222020698081638</v>
       </c>
       <c r="Q26" s="4">
         <v>0.0367233377877028</v>
@@ -14001,7 +14001,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="4">
-        <v>-0.1213046168050503</v>
+        <v>-0.1282741581161986</v>
       </c>
       <c r="O27" s="5">
         <v>14</v>
@@ -14060,7 +14060,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="4">
-        <v>-0.09258207352649654</v>
+        <v>-0.08948224889081757</v>
       </c>
       <c r="O28" s="5">
         <v>14</v>
@@ -14119,16 +14119,16 @@
         <v>0</v>
       </c>
       <c r="N29" s="4">
-        <v>-0.15201708037801</v>
+        <v>-0.1406020330895785</v>
       </c>
       <c r="O29" s="5">
         <v>14</v>
       </c>
       <c r="P29" s="4">
-        <v>0.06395419081375527</v>
+        <v>0.06284239726091455</v>
       </c>
       <c r="Q29" s="4">
-        <v>0.06395419081375527</v>
+        <v>0.06284239726091455</v>
       </c>
       <c r="R29" s="5">
         <v>14</v>
@@ -14178,16 +14178,16 @@
         <v>0</v>
       </c>
       <c r="N30" s="4">
-        <v>-0.3968345066581094</v>
+        <v>-0.3154497058700372</v>
       </c>
       <c r="O30" s="5">
         <v>7</v>
       </c>
       <c r="P30" s="4">
-        <v>0.5173681017666029</v>
+        <v>0.5458271652647925</v>
       </c>
       <c r="Q30" s="4">
-        <v>0.1673375817477612</v>
+        <v>0.1428709079560682</v>
       </c>
       <c r="R30" s="5">
         <v>7</v>
@@ -14237,16 +14237,16 @@
         <v>0</v>
       </c>
       <c r="N31" s="4">
-        <v>-0.3284528676557904</v>
+        <v>-0.3356110168161592</v>
       </c>
       <c r="O31" s="5">
         <v>9</v>
       </c>
       <c r="P31" s="4">
-        <v>0.1904616847858625</v>
+        <v>0.1873939065742758</v>
       </c>
       <c r="Q31" s="4">
-        <v>0.04126351188219492</v>
+        <v>0.04046816197548727</v>
       </c>
       <c r="R31" s="5">
         <v>9</v>
@@ -14296,16 +14296,16 @@
         <v>0</v>
       </c>
       <c r="N32" s="4">
-        <v>-0.06365231597489422</v>
+        <v>-0.07776558356431451</v>
       </c>
       <c r="O32" s="5">
         <v>12</v>
       </c>
       <c r="P32" s="4">
-        <v>0.05658675100945317</v>
+        <v>0.0525656640200834</v>
       </c>
       <c r="Q32" s="4">
-        <v>0.03443150031002023</v>
+        <v>0.03209244342065887</v>
       </c>
       <c r="R32" s="5">
         <v>12</v>
@@ -14588,16 +14588,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3767053955663968</v>
+        <v>0.3574016351537779</v>
       </c>
       <c r="O3" s="5">
         <v>32</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1076116186184706</v>
+        <v>0.1060831524145511</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1076116186184706</v>
+        <v>0.1060831524145511</v>
       </c>
       <c r="R3" s="5">
         <v>32</v>
@@ -14647,16 +14647,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3402723702790145</v>
+        <v>0.3515161449023481</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.260224143783531</v>
+        <v>0.2616879721083296</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.0812686881311101</v>
+        <v>0.07947253435639687</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -14759,16 +14759,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.4975256871528033</v>
+        <v>0.5129788688037138</v>
       </c>
       <c r="O6" s="5">
         <v>19</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2395792502627204</v>
+        <v>0.2403151160556209</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.08736286034285368</v>
+        <v>0.08654953499280575</v>
       </c>
       <c r="R6" s="5">
         <v>19</v>
@@ -14818,16 +14818,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.7329566104680282</v>
+        <v>0.743151211534439</v>
       </c>
       <c r="O7" s="5">
         <v>10</v>
       </c>
       <c r="P7" s="4">
-        <v>1.155742421157554</v>
+        <v>1.160155329668902</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.0792870356390597</v>
+        <v>0.07734008233983899</v>
       </c>
       <c r="R7" s="5">
         <v>10</v>
@@ -14877,16 +14877,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.5780177070052162</v>
+        <v>0.5821883870410289</v>
       </c>
       <c r="O8" s="5">
         <v>18</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2310058904713893</v>
+        <v>0.2308677506742972</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1164792111791099</v>
+        <v>0.1160863436360684</v>
       </c>
       <c r="R8" s="5">
         <v>18</v>
@@ -14936,16 +14936,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.5368999739516281</v>
+        <v>0.5564594089257469</v>
       </c>
       <c r="O9" s="5">
         <v>17</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2462247878333995</v>
+        <v>0.2490189928297022</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1152537195349</v>
+        <v>0.1141031645364224</v>
       </c>
       <c r="R9" s="5">
         <v>17</v>
@@ -14995,16 +14995,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.07908549145327613</v>
+        <v>0.1056095178710734</v>
       </c>
       <c r="O10" s="5">
         <v>19</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1316591467762602</v>
+        <v>0.1303960978992222</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1161481283119228</v>
+        <v>0.1147521269215124</v>
       </c>
       <c r="R10" s="5">
         <v>19</v>
@@ -15054,16 +15054,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.8199175933411251</v>
+        <v>-0.831981543608407</v>
       </c>
       <c r="O11" s="5">
         <v>19</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2872879319578253</v>
+        <v>0.2855645104910707</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1230298848290333</v>
+        <v>0.1223949400781237</v>
       </c>
       <c r="R11" s="5">
         <v>19</v>
@@ -15113,16 +15113,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.4897961276637594</v>
+        <v>-0.4660689424413818</v>
       </c>
       <c r="O12" s="5">
         <v>13</v>
       </c>
       <c r="P12" s="4">
-        <v>0.6754697049800723</v>
+        <v>0.682570895397604</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1052984636360492</v>
+        <v>0.1021682726352144</v>
       </c>
       <c r="R12" s="5">
         <v>13</v>
@@ -15172,16 +15172,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>1.020766623750006</v>
+        <v>1.006534918339838</v>
       </c>
       <c r="O13" s="5">
         <v>10</v>
       </c>
       <c r="P13" s="4">
-        <v>1.165016151035156</v>
+        <v>1.156967140956094</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1273216359843787</v>
+        <v>0.1260735907695335</v>
       </c>
       <c r="R13" s="5">
         <v>10</v>
@@ -15231,16 +15231,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.5888994231640604</v>
+        <v>-0.6260390163574243</v>
       </c>
       <c r="O14" s="5">
         <v>18</v>
       </c>
       <c r="P14" s="4">
-        <v>0.2690361043666262</v>
+        <v>0.2581933586639688</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1784803927614955</v>
+        <v>0.1720204549739558</v>
       </c>
       <c r="R14" s="5">
         <v>18</v>
@@ -15290,16 +15290,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>-0.6434280363154916</v>
+        <v>-0.6666766513281459</v>
       </c>
       <c r="O15" s="5">
         <v>17</v>
       </c>
       <c r="P15" s="4">
-        <v>0.2961171547354257</v>
+        <v>0.2890294754241046</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.1828553772885348</v>
+        <v>0.1795702710834097</v>
       </c>
       <c r="R15" s="5">
         <v>17</v>
@@ -15349,16 +15349,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.858335000957284</v>
+        <v>-0.9204390278661947</v>
       </c>
       <c r="O16" s="5">
         <v>19</v>
       </c>
       <c r="P16" s="4">
-        <v>0.179618985426596</v>
+        <v>0.1681233885063158</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.1728575887080632</v>
+        <v>0.166689194944481</v>
       </c>
       <c r="R16" s="5">
         <v>19</v>
@@ -15406,16 +15406,16 @@
         <v>10</v>
       </c>
       <c r="N17" s="4">
-        <v>2.402668530930649</v>
+        <v>2.436564799829085</v>
       </c>
       <c r="O17" s="5">
         <v>10</v>
       </c>
       <c r="P17" s="4">
-        <v>0.448548536976559</v>
+        <v>0.4578828295870494</v>
       </c>
       <c r="Q17" s="4">
-        <v>0.1066874157718712</v>
+        <v>0.1061969178671831</v>
       </c>
       <c r="R17" s="5">
         <v>10</v>
@@ -15465,16 +15465,16 @@
         <v>0</v>
       </c>
       <c r="N18" s="4">
-        <v>0.2934101254804659</v>
+        <v>0.1889477670117117</v>
       </c>
       <c r="O18" s="5">
         <v>5</v>
       </c>
       <c r="P18" s="4">
-        <v>0.4432655564129447</v>
+        <v>0.3835727801450852</v>
       </c>
       <c r="Q18" s="4">
-        <v>0.2809589735062537</v>
+        <v>0.2600665018125028</v>
       </c>
       <c r="R18" s="5">
         <v>5</v>
@@ -15524,16 +15524,16 @@
         <v>0</v>
       </c>
       <c r="N19" s="4">
-        <v>0.1148362065299414</v>
+        <v>0.1192837282226407</v>
       </c>
       <c r="O19" s="5">
         <v>12</v>
       </c>
       <c r="P19" s="4">
-        <v>0.05423906419085053</v>
+        <v>0.05469046399553739</v>
       </c>
       <c r="Q19" s="4">
-        <v>0.03609078526258753</v>
+        <v>0.03587616475260565</v>
       </c>
       <c r="R19" s="5">
         <v>12</v>
@@ -15583,16 +15583,16 @@
         <v>0</v>
       </c>
       <c r="N20" s="4">
-        <v>0.07329287228096908</v>
+        <v>0.08019502838865833</v>
       </c>
       <c r="O20" s="5">
         <v>14</v>
       </c>
       <c r="P20" s="4">
-        <v>0.03489064901904842</v>
+        <v>0.03437293957589255</v>
       </c>
       <c r="Q20" s="4">
-        <v>0.03489064901904842</v>
+        <v>0.03437293957589255</v>
       </c>
       <c r="R20" s="5">
         <v>14</v>
@@ -15642,16 +15642,16 @@
         <v>0</v>
       </c>
       <c r="N21" s="4">
-        <v>-0.01526741515625692</v>
+        <v>-0.00434070996094249</v>
       </c>
       <c r="O21" s="5">
         <v>12</v>
       </c>
       <c r="P21" s="4">
-        <v>0.06301199150669574</v>
+        <v>0.06127078544084595</v>
       </c>
       <c r="Q21" s="4">
-        <v>0.03287582376301993</v>
+        <v>0.02902329915364277</v>
       </c>
       <c r="R21" s="5">
         <v>12</v>
@@ -15701,13 +15701,13 @@
         <v>0</v>
       </c>
       <c r="N22" s="4">
-        <v>0.6287023812500045</v>
+        <v>0.6033560930078323</v>
       </c>
       <c r="O22" s="5">
         <v>8</v>
       </c>
       <c r="P22" s="4">
-        <v>0.3340846437890735</v>
+        <v>0.3232219488281426</v>
       </c>
       <c r="Q22" s="4">
         <v>0.0819200121484478</v>
@@ -15813,13 +15813,13 @@
         <v>0</v>
       </c>
       <c r="N24" s="4">
-        <v>0.5353315680165963</v>
+        <v>0.5186117389697245</v>
       </c>
       <c r="O24" s="5">
         <v>10</v>
       </c>
       <c r="P24" s="4">
-        <v>0.6860483332433027</v>
+        <v>0.6812712392299106</v>
       </c>
       <c r="Q24" s="4">
         <v>0.2220788292500004</v>
@@ -15872,16 +15872,16 @@
         <v>0</v>
       </c>
       <c r="N25" s="4">
-        <v>-0.7041537771549429</v>
+        <v>-0.7283555577392633</v>
       </c>
       <c r="O25" s="5">
         <v>12</v>
       </c>
       <c r="P25" s="4">
-        <v>0.1900901138148754</v>
+        <v>0.1811389446596</v>
       </c>
       <c r="Q25" s="4">
-        <v>0.141821794516062</v>
+        <v>0.1354123939322941</v>
       </c>
       <c r="R25" s="5">
         <v>12</v>
@@ -15931,16 +15931,16 @@
         <v>0</v>
       </c>
       <c r="N26" s="4">
-        <v>-0.6368214957828715</v>
+        <v>-0.6406376458349712</v>
       </c>
       <c r="O26" s="5">
         <v>9</v>
       </c>
       <c r="P26" s="4">
-        <v>0.3500642127157699</v>
+        <v>0.3489738841294557</v>
       </c>
       <c r="Q26" s="4">
-        <v>0.1894295725752275</v>
+        <v>0.189005555902772</v>
       </c>
       <c r="R26" s="5">
         <v>9</v>
@@ -15990,13 +15990,13 @@
         <v>0</v>
       </c>
       <c r="N27" s="4">
-        <v>0.4442874347737653</v>
+        <v>0.4106526396484327</v>
       </c>
       <c r="O27" s="5">
         <v>12</v>
       </c>
       <c r="P27" s="4">
-        <v>0.1521425078862061</v>
+        <v>0.1473375371540158</v>
       </c>
       <c r="Q27" s="4">
         <v>0.141100018248693</v>
@@ -16049,16 +16049,16 @@
         <v>0</v>
       </c>
       <c r="N28" s="4">
-        <v>0.4060391148437483</v>
+        <v>0.3735821091406137</v>
       </c>
       <c r="O28" s="5">
         <v>14</v>
       </c>
       <c r="P28" s="4">
-        <v>0.1347851786941972</v>
+        <v>0.1317556363839287</v>
       </c>
       <c r="Q28" s="4">
-        <v>0.1347851786941972</v>
+        <v>0.1317556363839287</v>
       </c>
       <c r="R28" s="5">
         <v>14</v>
@@ -16108,16 +16108,16 @@
         <v>0</v>
       </c>
       <c r="N29" s="4">
-        <v>-0.07522861828856502</v>
+        <v>-0.09341368945311501</v>
       </c>
       <c r="O29" s="5">
         <v>12</v>
       </c>
       <c r="P29" s="4">
-        <v>0.1383415302985462</v>
+        <v>0.1340845676109045</v>
       </c>
       <c r="Q29" s="4">
-        <v>0.1291721218143679</v>
+        <v>0.1272365105395442</v>
       </c>
       <c r="R29" s="5">
         <v>12</v>
@@ -16167,16 +16167,16 @@
         <v>0</v>
       </c>
       <c r="N30" s="4">
-        <v>-1.021204477062497</v>
+        <v>-1.027168958613288</v>
       </c>
       <c r="O30" s="5">
         <v>5</v>
       </c>
       <c r="P30" s="4">
-        <v>0.4586887490090663</v>
+        <v>0.4552804738371857</v>
       </c>
       <c r="Q30" s="4">
-        <v>0.3053048257007845</v>
+        <v>0.3041119293906263</v>
       </c>
       <c r="R30" s="5">
         <v>5</v>
@@ -16226,16 +16226,16 @@
         <v>0</v>
       </c>
       <c r="N31" s="4">
-        <v>-0.3872876607788136</v>
+        <v>-0.341663486249999</v>
       </c>
       <c r="O31" s="5">
         <v>8</v>
       </c>
       <c r="P31" s="4">
-        <v>0.3200056635930518</v>
+        <v>0.3348283007184725</v>
       </c>
       <c r="Q31" s="4">
-        <v>0.1746566771844487</v>
+        <v>0.1663781612573239</v>
       </c>
       <c r="R31" s="5">
         <v>8</v>
@@ -16285,16 +16285,16 @@
         <v>0</v>
       </c>
       <c r="N32" s="4">
-        <v>-0.4050861479521444</v>
+        <v>-0.4186697394335965</v>
       </c>
       <c r="O32" s="5">
         <v>10</v>
       </c>
       <c r="P32" s="4">
-        <v>0.1753558225079534</v>
+        <v>0.1744176679045779</v>
       </c>
       <c r="Q32" s="4">
-        <v>0.1490953584710928</v>
+        <v>0.1477819420263671</v>
       </c>
       <c r="R32" s="5">
         <v>10</v>
@@ -16575,16 +16575,16 @@
         <v>32</v>
       </c>
       <c r="N3" s="4">
-        <v>4.419341313229971</v>
+        <v>4.408655589981677</v>
       </c>
       <c r="O3" s="5">
         <v>32</v>
       </c>
       <c r="P3" s="4">
-        <v>0.07237302615432917</v>
+        <v>0.07174682709594915</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.07237302615432917</v>
+        <v>0.07174682709594915</v>
       </c>
       <c r="R3" s="5">
         <v>32</v>
@@ -16634,16 +16634,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2416768827434055</v>
+        <v>0.232063726804185</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2478903166302514</v>
+        <v>0.2449375058189166</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.0905207493190204</v>
+        <v>0.09023207655883994</v>
       </c>
       <c r="R4" s="5">
         <v>20</v>
@@ -16693,13 +16693,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3120725786892409</v>
+        <v>0.3131733732422077</v>
       </c>
       <c r="O5" s="5">
         <v>18</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3518722166449678</v>
+        <v>0.3520294730096773</v>
       </c>
       <c r="Q5" s="4">
         <v>0.1253618794444485</v>
@@ -16752,16 +16752,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.4820396383019289</v>
+        <v>0.4886002109375056</v>
       </c>
       <c r="O6" s="5">
         <v>17</v>
       </c>
       <c r="P6" s="4">
-        <v>0.4472249518741276</v>
+        <v>0.4480573701618361</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1028723963635377</v>
+        <v>0.1023570136282183</v>
       </c>
       <c r="R6" s="5">
         <v>17</v>
@@ -16811,13 +16811,13 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.6745048916017465</v>
+        <v>0.6925761108483925</v>
       </c>
       <c r="O7" s="5">
         <v>14</v>
       </c>
       <c r="P7" s="4">
-        <v>0.8526512992912976</v>
+        <v>0.8586750390401796</v>
       </c>
       <c r="Q7" s="4">
         <v>0.09766092895647407</v>
@@ -16870,16 +16870,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.6650287931022171</v>
+        <v>0.6741404899511707</v>
       </c>
       <c r="O8" s="5">
         <v>18</v>
       </c>
       <c r="P8" s="4">
-        <v>0.08002521450086324</v>
+        <v>0.08046677781435378</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.06039502478877121</v>
+        <v>0.05939156584635125</v>
       </c>
       <c r="R8" s="5">
         <v>18</v>
@@ -16929,16 +16929,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.6267726572387655</v>
+        <v>0.6298002532812603</v>
       </c>
       <c r="O9" s="5">
         <v>16</v>
       </c>
       <c r="P9" s="4">
-        <v>0.09080277609643068</v>
+        <v>0.09137607622117676</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.05811310404145265</v>
+        <v>0.05791943669190225</v>
       </c>
       <c r="R9" s="5">
         <v>16</v>
@@ -16988,16 +16988,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.4949587859678767</v>
+        <v>0.5070427869335958</v>
       </c>
       <c r="O10" s="5">
         <v>18</v>
       </c>
       <c r="P10" s="4">
-        <v>0.07327966019582187</v>
+        <v>0.07417277033481523</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.06112316414158545</v>
+        <v>0.06015112580945785</v>
       </c>
       <c r="R10" s="5">
         <v>18</v>
@@ -17047,16 +17047,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.1043799016073024</v>
+        <v>-0.08314135544921442</v>
       </c>
       <c r="O11" s="5">
         <v>17</v>
       </c>
       <c r="P11" s="4">
-        <v>0.4578346928764001</v>
+        <v>0.4589610243898817</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.108655306316497</v>
+        <v>0.1050493520312477</v>
       </c>
       <c r="R11" s="5">
         <v>17</v>
@@ -17106,16 +17106,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.04554137000542053</v>
+        <v>-0.02089767258786424</v>
       </c>
       <c r="O12" s="5">
         <v>18</v>
       </c>
       <c r="P12" s="4">
-        <v>0.3593880640571287</v>
+        <v>0.3612438510881732</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1190104089535152</v>
+        <v>0.1170682109201411</v>
       </c>
       <c r="R12" s="5">
         <v>18</v>
@@ -17165,13 +17165,13 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.1138413349992951</v>
+        <v>-0.09110383754394036</v>
       </c>
       <c r="O13" s="5">
         <v>14</v>
       </c>
       <c r="P13" s="4">
-        <v>0.8821139911179261</v>
+        <v>0.8896931569363777</v>
       </c>
       <c r="Q13" s="4">
         <v>0.1067119034207532</v>
@@ -17224,16 +17224,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.04927187442491111</v>
+        <v>-0.04533459146972518</v>
       </c>
       <c r="O14" s="5">
         <v>18</v>
       </c>
       <c r="P14" s="4">
-        <v>0.09854759208979127</v>
+        <v>0.09876755220028463</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1004204632998134</v>
+        <v>0.1000208696028579</v>
       </c>
       <c r="R14" s="5">
         <v>18</v>
@@ -17283,16 +17283,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>-0.04771758023193584</v>
+        <v>-0.04001294319824922</v>
       </c>
       <c r="O15" s="5">
         <v>16</v>
       </c>
       <c r="P15" s="4">
-        <v>0.1126102821208901</v>
+        <v>0.11407480705474</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.1003335439462316</v>
+        <v>0.09984803384888252</v>
       </c>
       <c r="R15" s="5">
         <v>16</v>
@@ -17342,16 +17342,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.1525590364404271</v>
+        <v>-0.1426971649365356</v>
       </c>
       <c r="O16" s="5">
         <v>18</v>
       </c>
       <c r="P16" s="4">
-        <v>0.09197523217354575</v>
+        <v>0.09262443701264138</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.1010778078211769</v>
+        <v>0.1005366904882787</v>
       </c>
       <c r="R16" s="5">
         <v>18</v>
@@ -17399,16 +17399,16 @@
         <v>13</v>
       </c>
       <c r="N17" s="4">
-        <v>6.771848744136197</v>
+        <v>6.786719994635007</v>
       </c>
       <c r="O17" s="5">
         <v>13</v>
       </c>
       <c r="P17" s="4">
-        <v>0.2052765267007161</v>
+        <v>0.2045132316071374</v>
       </c>
       <c r="Q17" s="4">
-        <v>0.08478691388313155</v>
+        <v>0.08282096143629211</v>
       </c>
       <c r="R17" s="5">
         <v>13</v>
@@ -17515,16 +17515,16 @@
         <v>0</v>
       </c>
       <c r="N19" s="4">
-        <v>0.2023174492103712</v>
+        <v>0.2110958620117032</v>
       </c>
       <c r="O19" s="5">
         <v>14</v>
       </c>
       <c r="P19" s="4">
-        <v>0.04545316494260399</v>
+        <v>0.04516023406808399</v>
       </c>
       <c r="Q19" s="4">
-        <v>0.04545316494260399</v>
+        <v>0.04516023406808399</v>
       </c>
       <c r="R19" s="5">
         <v>14</v>
@@ -17574,16 +17574,16 @@
         <v>0</v>
       </c>
       <c r="N20" s="4">
-        <v>0.1416037461300204</v>
+        <v>0.136576727832022</v>
       </c>
       <c r="O20" s="5">
         <v>14</v>
       </c>
       <c r="P20" s="4">
-        <v>0.02680959601243778</v>
+        <v>0.02618456607701043</v>
       </c>
       <c r="Q20" s="4">
-        <v>0.02680959601243778</v>
+        <v>0.02618456607701043</v>
       </c>
       <c r="R20" s="5">
         <v>14</v>
@@ -17633,16 +17633,16 @@
         <v>0</v>
       </c>
       <c r="N21" s="4">
-        <v>0.1076689377950544</v>
+        <v>0.1134035404736267</v>
       </c>
       <c r="O21" s="5">
         <v>14</v>
       </c>
       <c r="P21" s="4">
-        <v>0.03378746989158036</v>
+        <v>0.03313235164620413</v>
       </c>
       <c r="Q21" s="4">
-        <v>0.03378746989158036</v>
+        <v>0.03313235164620413</v>
       </c>
       <c r="R21" s="5">
         <v>14</v>
@@ -17692,16 +17692,16 @@
         <v>0</v>
       </c>
       <c r="N22" s="4">
-        <v>0.2482612653320307</v>
+        <v>0.2319320017968778</v>
       </c>
       <c r="O22" s="5">
         <v>12</v>
       </c>
       <c r="P22" s="4">
-        <v>0.1391905671735501</v>
+        <v>0.1348137003013384</v>
       </c>
       <c r="Q22" s="4">
-        <v>0.08391295125000102</v>
+        <v>0.08152815048827951</v>
       </c>
       <c r="R22" s="5">
         <v>12</v>
@@ -17751,7 +17751,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="4">
-        <v>0.3109055531144892</v>
+        <v>0.3571703137695579</v>
       </c>
       <c r="O23" s="5">
         <v>13</v>
@@ -17760,7 +17760,7 @@
         <v>0.08090967386162008</v>
       </c>
       <c r="Q23" s="4">
-        <v>0.08274587874631346</v>
+        <v>0.07918705100361588</v>
       </c>
       <c r="R23" s="5">
         <v>13</v>
@@ -17810,7 +17810,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="4">
-        <v>-0.4949225705322314</v>
+        <v>-0.460889739619148</v>
       </c>
       <c r="O24" s="5">
         <v>13</v>
@@ -17819,7 +17819,7 @@
         <v>0.2243114247042359</v>
       </c>
       <c r="Q24" s="4">
-        <v>0.1035793470413865</v>
+        <v>0.1009614369711493</v>
       </c>
       <c r="R24" s="5">
         <v>13</v>
@@ -17869,16 +17869,16 @@
         <v>0</v>
       </c>
       <c r="N25" s="4">
-        <v>-0.3492657579991266</v>
+        <v>-0.292636195195314</v>
       </c>
       <c r="O25" s="5">
         <v>9</v>
       </c>
       <c r="P25" s="4">
-        <v>0.2814378776064179</v>
+        <v>0.2976177526932214</v>
       </c>
       <c r="Q25" s="4">
-        <v>0.0953927935233443</v>
+        <v>0.08910061987847623</v>
       </c>
       <c r="R25" s="5">
         <v>9</v>
@@ -17928,13 +17928,13 @@
         <v>0</v>
       </c>
       <c r="N26" s="4">
-        <v>-0.375685082041007</v>
+        <v>-0.3557748397558527</v>
       </c>
       <c r="O26" s="5">
         <v>12</v>
       </c>
       <c r="P26" s="4">
-        <v>0.1830325199860439</v>
+        <v>0.1858768403124945</v>
       </c>
       <c r="Q26" s="4">
         <v>0.08924293055337766</v>
@@ -17987,16 +17987,16 @@
         <v>0</v>
       </c>
       <c r="N27" s="4">
-        <v>-0.008594285637556709</v>
+        <v>0.01246863942382959</v>
       </c>
       <c r="O27" s="5">
         <v>14</v>
       </c>
       <c r="P27" s="4">
-        <v>0.06501707720503346</v>
+        <v>0.06187277764508435</v>
       </c>
       <c r="Q27" s="4">
-        <v>0.06501707720503346</v>
+        <v>0.06187277764508435</v>
       </c>
       <c r="R27" s="5">
         <v>14</v>
@@ -18046,16 +18046,16 @@
         <v>0</v>
       </c>
       <c r="N28" s="4">
-        <v>-0.0796802934640084</v>
+        <v>-0.06139708516603548</v>
       </c>
       <c r="O28" s="5">
         <v>14</v>
       </c>
       <c r="P28" s="4">
-        <v>0.04715470613201741</v>
+        <v>0.04452247794642972</v>
       </c>
       <c r="Q28" s="4">
-        <v>0.04715470613201741</v>
+        <v>0.04452247794642972</v>
       </c>
       <c r="R28" s="5">
         <v>14</v>
@@ -18105,7 +18105,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="4">
-        <v>-0.273675101696071</v>
+        <v>-0.2750090163769414</v>
       </c>
       <c r="O29" s="5">
         <v>14</v>
@@ -18221,13 +18221,13 @@
         <v>0</v>
       </c>
       <c r="N31" s="4">
-        <v>-0.2817880046549514</v>
+        <v>-0.2686926193164112</v>
       </c>
       <c r="O31" s="5">
         <v>12</v>
       </c>
       <c r="P31" s="4">
-        <v>0.145541598076638</v>
+        <v>0.1474123674107151</v>
       </c>
       <c r="Q31" s="4">
         <v>0.09464399402343797</v>
@@ -18280,7 +18280,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="4">
-        <v>-0.08248180388896852</v>
+        <v>-0.05224123645504619</v>
       </c>
       <c r="O32" s="5">
         <v>13</v>
@@ -18289,7 +18289,7 @@
         <v>0.09824152624442409</v>
       </c>
       <c r="Q32" s="4">
-        <v>0.09967718745285052</v>
+        <v>0.09735098995793343</v>
       </c>
       <c r="R32" s="5">
         <v>13</v>
